--- a/comp_sum_select.xlsx
+++ b/comp_sum_select.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LRMLD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4BD431-72B4-4BA0-B457-E57EC4A6F642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D471B1-746B-41A7-A1A6-FEC32D5AC0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="74">
   <si>
     <t>LUT</t>
   </si>
@@ -304,29 +304,12 @@
 LLR_W = 6</t>
   </si>
   <si>
-    <t>RM(32,11)</t>
-  </si>
-  <si>
-    <t>IS_FSM = 0
-LLR_W = 8</t>
-  </si>
-  <si>
     <t>IS_FSM = 2
 LLR_W = 6</t>
   </si>
   <si>
     <t>IS_FSM = 3
 LLR_W = 6</t>
-  </si>
-  <si>
-    <t>IS_FSM = 3
-LLR_W = 8</t>
-  </si>
-  <si>
-    <t>N = 64</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Задержка, 
@@ -423,7 +406,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,18 +415,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="73">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1278,59 +1255,7 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -1342,28 +1267,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1373,7 +1276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1558,43 +1461,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1606,226 +1473,211 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2108,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D1:AY143"/>
+  <dimension ref="D1:AZ143"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="8.88671875" style="1"/>
@@ -2135,177 +1987,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
     </row>
     <row r="2" spans="4:31" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="H3" s="140" t="s">
+      <c r="H3" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132" t="s">
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="128" t="s">
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="129"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="125" t="s">
+      <c r="O3" s="111"/>
+      <c r="P3" s="112"/>
+      <c r="Q3" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="126"/>
-      <c r="S3" s="126"/>
-      <c r="T3" s="126" t="s">
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="126"/>
-      <c r="V3" s="133"/>
-      <c r="W3" s="127" t="s">
+      <c r="U3" s="108"/>
+      <c r="V3" s="114"/>
+      <c r="W3" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="X3" s="126"/>
-      <c r="Y3" s="126"/>
-      <c r="Z3" s="114" t="s">
+      <c r="X3" s="108"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="AA3" s="115"/>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="114" t="s">
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="AD3" s="115"/>
-      <c r="AE3" s="116"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="120"/>
     </row>
     <row r="4" spans="4:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="139" t="s">
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136" t="s">
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="136"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="137" t="s">
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="113"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="135" t="s">
+      <c r="O4" s="97"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="113" t="s">
+      <c r="R4" s="101"/>
+      <c r="S4" s="101"/>
+      <c r="T4" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="113"/>
-      <c r="V4" s="134"/>
-      <c r="W4" s="124" t="s">
+      <c r="U4" s="97"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="X4" s="108"/>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="117" t="s">
+      <c r="X4" s="101"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="119"/>
-      <c r="AC4" s="117" t="s">
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="123"/>
+      <c r="AC4" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="AD4" s="118"/>
-      <c r="AE4" s="119"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="123"/>
     </row>
     <row r="5" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="139"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
-      <c r="M5" s="136"/>
-      <c r="N5" s="137"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="135"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="124"/>
-      <c r="X5" s="108"/>
-      <c r="Y5" s="108"/>
-      <c r="Z5" s="120"/>
-      <c r="AA5" s="84"/>
-      <c r="AB5" s="88"/>
-      <c r="AC5" s="120"/>
-      <c r="AD5" s="84"/>
-      <c r="AE5" s="88"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="116"/>
+      <c r="O5" s="97"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="101"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="97"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="128"/>
+      <c r="X5" s="101"/>
+      <c r="Y5" s="101"/>
+      <c r="Z5" s="124"/>
+      <c r="AA5" s="74"/>
+      <c r="AB5" s="71"/>
+      <c r="AC5" s="124"/>
+      <c r="AD5" s="74"/>
+      <c r="AE5" s="71"/>
     </row>
     <row r="6" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="113"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="113"/>
-      <c r="U6" s="113"/>
-      <c r="V6" s="134"/>
-      <c r="W6" s="124"/>
-      <c r="X6" s="108"/>
-      <c r="Y6" s="108"/>
-      <c r="Z6" s="121"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="123"/>
-      <c r="AC6" s="121"/>
-      <c r="AD6" s="122"/>
-      <c r="AE6" s="123"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="116"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="101"/>
+      <c r="S6" s="101"/>
+      <c r="T6" s="97"/>
+      <c r="U6" s="97"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="128"/>
+      <c r="X6" s="101"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="125"/>
+      <c r="AA6" s="126"/>
+      <c r="AB6" s="127"/>
+      <c r="AC6" s="125"/>
+      <c r="AD6" s="126"/>
+      <c r="AE6" s="127"/>
     </row>
     <row r="7" spans="4:31" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="D7" s="108" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108" t="s">
+      <c r="D7" s="101" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="109"/>
+      <c r="G7" s="102"/>
       <c r="H7" s="11" t="s">
         <v>0</v>
       </c>
@@ -2380,14 +2232,14 @@
       </c>
     </row>
     <row r="8" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D8" s="108">
-        <v>8</v>
-      </c>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108">
-        <v>8</v>
-      </c>
-      <c r="G8" s="109"/>
+      <c r="D8" s="101">
+        <v>8</v>
+      </c>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101">
+        <v>8</v>
+      </c>
+      <c r="G8" s="102"/>
       <c r="H8" s="11">
         <v>331</v>
       </c>
@@ -2462,14 +2314,14 @@
       </c>
     </row>
     <row r="9" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D9" s="108">
+      <c r="D9" s="101">
         <v>10</v>
       </c>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108">
+      <c r="E9" s="101"/>
+      <c r="F9" s="101">
         <v>16</v>
       </c>
-      <c r="G9" s="109"/>
+      <c r="G9" s="102"/>
       <c r="H9" s="11">
         <v>504</v>
       </c>
@@ -2544,14 +2396,14 @@
       </c>
     </row>
     <row r="10" spans="4:31" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D10" s="108">
+      <c r="D10" s="101">
         <v>10</v>
       </c>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108">
+      <c r="E10" s="101"/>
+      <c r="F10" s="101">
         <v>32</v>
       </c>
-      <c r="G10" s="109"/>
+      <c r="G10" s="102"/>
       <c r="H10" s="13">
         <v>761</v>
       </c>
@@ -2626,17 +2478,17 @@
       </c>
     </row>
     <row r="11" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="H11" s="131" t="s">
+      <c r="H11" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="131"/>
-      <c r="N11" s="131"/>
-      <c r="O11" s="131"/>
-      <c r="P11" s="131"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="113"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="113"/>
+      <c r="O11" s="113"/>
+      <c r="P11" s="113"/>
     </row>
     <row r="12" spans="4:31" ht="23.4" x14ac:dyDescent="0.3">
       <c r="O12" s="19" t="s">
@@ -2644,103 +2496,103 @@
       </c>
     </row>
     <row r="13" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="N13" s="84" t="s">
+      <c r="N13" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="O13" s="84"/>
-      <c r="P13" s="84"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
     </row>
     <row r="14" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="N14" s="84"/>
-      <c r="O14" s="84"/>
-      <c r="P14" s="84"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
     </row>
     <row r="15" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="N15" s="84"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="84"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
     </row>
     <row r="17" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="H17" s="108" t="s">
+      <c r="H17" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="108"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="108" t="s">
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="108"/>
-      <c r="M17" s="108"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="101"/>
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17"/>
     </row>
     <row r="18" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="H18" s="113" t="s">
+      <c r="H18" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="113"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="113" t="s">
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="S18" s="113" t="s">
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="S18" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="T18" s="113"/>
-      <c r="U18" s="113"/>
-      <c r="AA18" s="113" t="s">
+      <c r="T18" s="97"/>
+      <c r="U18" s="97"/>
+      <c r="AA18" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="AB18" s="113"/>
-      <c r="AC18" s="113"/>
-      <c r="AH18" s="113" t="s">
+      <c r="AB18" s="97"/>
+      <c r="AC18" s="97"/>
+      <c r="AH18" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="AI18" s="113"/>
-      <c r="AJ18" s="113"/>
+      <c r="AI18" s="97"/>
+      <c r="AJ18" s="97"/>
     </row>
     <row r="19" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="H19" s="113"/>
-      <c r="I19" s="113"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="113"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="113"/>
-      <c r="S19" s="113"/>
-      <c r="T19" s="113"/>
-      <c r="U19" s="113"/>
-      <c r="AA19" s="113"/>
-      <c r="AB19" s="113"/>
-      <c r="AC19" s="113"/>
-      <c r="AH19" s="113"/>
-      <c r="AI19" s="113"/>
-      <c r="AJ19" s="113"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="S19" s="97"/>
+      <c r="T19" s="97"/>
+      <c r="U19" s="97"/>
+      <c r="AA19" s="97"/>
+      <c r="AB19" s="97"/>
+      <c r="AC19" s="97"/>
+      <c r="AH19" s="97"/>
+      <c r="AI19" s="97"/>
+      <c r="AJ19" s="97"/>
     </row>
     <row r="20" spans="5:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H20" s="113"/>
-      <c r="I20" s="113"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="113"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="113"/>
-      <c r="S20" s="113"/>
-      <c r="T20" s="113"/>
-      <c r="U20" s="113"/>
-      <c r="AA20" s="113"/>
-      <c r="AB20" s="113"/>
-      <c r="AC20" s="113"/>
-      <c r="AH20" s="113"/>
-      <c r="AI20" s="113"/>
-      <c r="AJ20" s="113"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="97"/>
+      <c r="S20" s="97"/>
+      <c r="T20" s="97"/>
+      <c r="U20" s="97"/>
+      <c r="AA20" s="97"/>
+      <c r="AB20" s="97"/>
+      <c r="AC20" s="97"/>
+      <c r="AH20" s="97"/>
+      <c r="AI20" s="97"/>
+      <c r="AJ20" s="97"/>
     </row>
     <row r="21" spans="5:36" ht="36" x14ac:dyDescent="0.3">
-      <c r="E21" s="113" t="s">
+      <c r="E21" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="113"/>
+      <c r="F21" s="97"/>
       <c r="G21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2762,10 +2614,10 @@
       <c r="M21" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="O21" s="113" t="s">
+      <c r="O21" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="P21" s="113"/>
+      <c r="P21" s="97"/>
       <c r="Q21" s="18" t="s">
         <v>33</v>
       </c>
@@ -2782,10 +2634,10 @@
         <v>2</v>
       </c>
       <c r="W21"/>
-      <c r="X21" s="113" t="s">
+      <c r="X21" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="Y21" s="113"/>
+      <c r="Y21" s="97"/>
       <c r="Z21" s="2" t="s">
         <v>31</v>
       </c>
@@ -2798,10 +2650,10 @@
       <c r="AC21" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AE21" s="113" t="s">
+      <c r="AE21" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="AF21" s="113"/>
+      <c r="AF21" s="97"/>
       <c r="AG21" s="18" t="s">
         <v>38</v>
       </c>
@@ -2816,8 +2668,8 @@
       </c>
     </row>
     <row r="22" spans="5:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E22" s="113"/>
-      <c r="F22" s="113"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="97"/>
       <c r="G22" s="2">
         <v>4</v>
       </c>
@@ -2839,8 +2691,8 @@
       <c r="M22" s="2">
         <v>578</v>
       </c>
-      <c r="O22" s="113"/>
-      <c r="P22" s="113"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="97"/>
       <c r="Q22" s="18">
         <v>8</v>
       </c>
@@ -2857,8 +2709,8 @@
         <v>455</v>
       </c>
       <c r="W22"/>
-      <c r="X22" s="113"/>
-      <c r="Y22" s="113"/>
+      <c r="X22" s="97"/>
+      <c r="Y22" s="97"/>
       <c r="Z22" s="2">
         <v>4</v>
       </c>
@@ -2871,8 +2723,8 @@
       <c r="AC22" s="2">
         <v>555</v>
       </c>
-      <c r="AE22" s="113"/>
-      <c r="AF22" s="113"/>
+      <c r="AE22" s="97"/>
+      <c r="AF22" s="97"/>
       <c r="AG22" s="2">
         <v>2</v>
       </c>
@@ -2887,8 +2739,8 @@
       </c>
     </row>
     <row r="23" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="E23" s="113"/>
-      <c r="F23" s="113"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="97"/>
       <c r="G23" s="2">
         <v>8</v>
       </c>
@@ -2910,8 +2762,8 @@
       <c r="M23" s="2">
         <v>476</v>
       </c>
-      <c r="O23" s="113"/>
-      <c r="P23" s="113"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="97"/>
       <c r="Q23" s="18">
         <v>12</v>
       </c>
@@ -2928,8 +2780,8 @@
         <v>462</v>
       </c>
       <c r="W23"/>
-      <c r="X23" s="113"/>
-      <c r="Y23" s="113"/>
+      <c r="X23" s="97"/>
+      <c r="Y23" s="97"/>
       <c r="Z23" s="2">
         <v>8</v>
       </c>
@@ -2942,8 +2794,8 @@
       <c r="AC23" s="2">
         <v>542</v>
       </c>
-      <c r="AE23" s="113"/>
-      <c r="AF23" s="113"/>
+      <c r="AE23" s="97"/>
+      <c r="AF23" s="97"/>
       <c r="AG23" s="2">
         <v>4</v>
       </c>
@@ -2958,8 +2810,8 @@
       </c>
     </row>
     <row r="24" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="E24" s="113"/>
-      <c r="F24" s="113"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="97"/>
       <c r="G24" s="2">
         <v>16</v>
       </c>
@@ -2981,8 +2833,8 @@
       <c r="M24" s="2">
         <v>387</v>
       </c>
-      <c r="O24" s="113"/>
-      <c r="P24" s="113"/>
+      <c r="O24" s="97"/>
+      <c r="P24" s="97"/>
       <c r="Q24" s="18">
         <v>16</v>
       </c>
@@ -2999,8 +2851,8 @@
         <v>390</v>
       </c>
       <c r="W24"/>
-      <c r="X24" s="113"/>
-      <c r="Y24" s="113"/>
+      <c r="X24" s="97"/>
+      <c r="Y24" s="97"/>
       <c r="Z24" s="2">
         <v>16</v>
       </c>
@@ -3013,8 +2865,8 @@
       <c r="AC24" s="2">
         <v>493</v>
       </c>
-      <c r="AE24" s="113"/>
-      <c r="AF24" s="113"/>
+      <c r="AE24" s="97"/>
+      <c r="AF24" s="97"/>
       <c r="AG24" s="2">
         <v>8</v>
       </c>
@@ -3030,80 +2882,80 @@
     </row>
     <row r="26" spans="5:36" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="E27" s="90" t="s">
+      <c r="E27" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="91"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="92"/>
-      <c r="S27" s="90" t="s">
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
+      <c r="L27" s="89"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="90"/>
+      <c r="S27" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="T27" s="91"/>
-      <c r="U27" s="91"/>
-      <c r="V27" s="91"/>
-      <c r="W27" s="91"/>
-      <c r="X27" s="91"/>
-      <c r="Y27" s="91"/>
-      <c r="Z27" s="91"/>
-      <c r="AA27" s="91"/>
-      <c r="AB27" s="92"/>
+      <c r="T27" s="89"/>
+      <c r="U27" s="89"/>
+      <c r="V27" s="89"/>
+      <c r="W27" s="89"/>
+      <c r="X27" s="89"/>
+      <c r="Y27" s="89"/>
+      <c r="Z27" s="89"/>
+      <c r="AA27" s="89"/>
+      <c r="AB27" s="90"/>
     </row>
     <row r="28" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="E28" s="93"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="94"/>
-      <c r="L28" s="94"/>
-      <c r="M28" s="94"/>
-      <c r="N28" s="95"/>
-      <c r="S28" s="93"/>
-      <c r="T28" s="94"/>
-      <c r="U28" s="94"/>
-      <c r="V28" s="94"/>
-      <c r="W28" s="94"/>
-      <c r="X28" s="94"/>
-      <c r="Y28" s="94"/>
-      <c r="Z28" s="94"/>
-      <c r="AA28" s="94"/>
-      <c r="AB28" s="95"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92"/>
+      <c r="L28" s="92"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="93"/>
+      <c r="S28" s="91"/>
+      <c r="T28" s="92"/>
+      <c r="U28" s="92"/>
+      <c r="V28" s="92"/>
+      <c r="W28" s="92"/>
+      <c r="X28" s="92"/>
+      <c r="Y28" s="92"/>
+      <c r="Z28" s="92"/>
+      <c r="AA28" s="92"/>
+      <c r="AB28" s="93"/>
     </row>
     <row r="29" spans="5:36" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E29" s="96"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="97"/>
-      <c r="N29" s="98"/>
-      <c r="S29" s="96"/>
-      <c r="T29" s="97"/>
-      <c r="U29" s="97"/>
-      <c r="V29" s="97"/>
-      <c r="W29" s="97"/>
-      <c r="X29" s="97"/>
-      <c r="Y29" s="97"/>
-      <c r="Z29" s="97"/>
-      <c r="AA29" s="97"/>
-      <c r="AB29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="99"/>
+      <c r="H29" s="99"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="99"/>
+      <c r="K29" s="99"/>
+      <c r="L29" s="99"/>
+      <c r="M29" s="99"/>
+      <c r="N29" s="100"/>
+      <c r="S29" s="98"/>
+      <c r="T29" s="99"/>
+      <c r="U29" s="99"/>
+      <c r="V29" s="99"/>
+      <c r="W29" s="99"/>
+      <c r="X29" s="99"/>
+      <c r="Y29" s="99"/>
+      <c r="Z29" s="99"/>
+      <c r="AA29" s="99"/>
+      <c r="AB29" s="100"/>
     </row>
     <row r="30" spans="5:36" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E30" s="81" t="s">
+      <c r="E30" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="87"/>
+      <c r="F30" s="69"/>
       <c r="G30" s="24" t="s">
         <v>33</v>
       </c>
@@ -3128,10 +2980,10 @@
       <c r="N30" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="S30" s="81" t="s">
+      <c r="S30" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="T30" s="87"/>
+      <c r="T30" s="69"/>
       <c r="U30" s="24" t="s">
         <v>33</v>
       </c>
@@ -3158,8 +3010,8 @@
       </c>
     </row>
     <row r="31" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="E31" s="83"/>
-      <c r="F31" s="88"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="71"/>
       <c r="G31" s="23">
         <v>4</v>
       </c>
@@ -3184,8 +3036,8 @@
       <c r="N31" s="5">
         <v>479</v>
       </c>
-      <c r="S31" s="83"/>
-      <c r="T31" s="88"/>
+      <c r="S31" s="70"/>
+      <c r="T31" s="71"/>
       <c r="U31" s="23">
         <v>4</v>
       </c>
@@ -3212,8 +3064,8 @@
       </c>
     </row>
     <row r="32" spans="5:36" x14ac:dyDescent="0.3">
-      <c r="E32" s="83"/>
-      <c r="F32" s="88"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="71"/>
       <c r="G32" s="23">
         <v>4</v>
       </c>
@@ -3238,8 +3090,8 @@
       <c r="N32" s="5">
         <v>300</v>
       </c>
-      <c r="S32" s="83"/>
-      <c r="T32" s="88"/>
+      <c r="S32" s="70"/>
+      <c r="T32" s="71"/>
       <c r="U32" s="23">
         <v>4</v>
       </c>
@@ -3266,8 +3118,8 @@
       </c>
     </row>
     <row r="33" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E33" s="83"/>
-      <c r="F33" s="88"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71"/>
       <c r="G33" s="23">
         <v>4</v>
       </c>
@@ -3292,8 +3144,8 @@
       <c r="N33" s="5">
         <v>276</v>
       </c>
-      <c r="S33" s="83"/>
-      <c r="T33" s="88"/>
+      <c r="S33" s="70"/>
+      <c r="T33" s="71"/>
       <c r="U33" s="23">
         <v>4</v>
       </c>
@@ -3320,8 +3172,8 @@
       </c>
     </row>
     <row r="34" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E34" s="83"/>
-      <c r="F34" s="88"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="71"/>
       <c r="G34" s="23">
         <v>4</v>
       </c>
@@ -3346,8 +3198,8 @@
       <c r="N34" s="5">
         <v>290</v>
       </c>
-      <c r="S34" s="83"/>
-      <c r="T34" s="88"/>
+      <c r="S34" s="70"/>
+      <c r="T34" s="71"/>
       <c r="U34" s="23">
         <v>4</v>
       </c>
@@ -3374,8 +3226,8 @@
       </c>
     </row>
     <row r="35" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E35" s="83"/>
-      <c r="F35" s="88"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71"/>
       <c r="G35" s="23">
         <v>8</v>
       </c>
@@ -3400,8 +3252,8 @@
       <c r="N35" s="5">
         <v>320</v>
       </c>
-      <c r="S35" s="83"/>
-      <c r="T35" s="88"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="71"/>
       <c r="U35" s="23">
         <v>8</v>
       </c>
@@ -3428,8 +3280,8 @@
       </c>
     </row>
     <row r="36" spans="5:31" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E36" s="83"/>
-      <c r="F36" s="88"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="71"/>
       <c r="G36" s="23">
         <v>8</v>
       </c>
@@ -3454,8 +3306,8 @@
       <c r="N36" s="5">
         <v>291</v>
       </c>
-      <c r="S36" s="83"/>
-      <c r="T36" s="88"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="71"/>
       <c r="U36" s="23">
         <v>8</v>
       </c>
@@ -3482,8 +3334,8 @@
       </c>
     </row>
     <row r="37" spans="5:31" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E37" s="85"/>
-      <c r="F37" s="89"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="73"/>
       <c r="G37" s="25">
         <v>12</v>
       </c>
@@ -3509,8 +3361,8 @@
         <v>304</v>
       </c>
       <c r="Q37"/>
-      <c r="S37" s="85"/>
-      <c r="T37" s="89"/>
+      <c r="S37" s="72"/>
+      <c r="T37" s="73"/>
       <c r="U37" s="25">
         <v>12</v>
       </c>
@@ -3535,16 +3387,16 @@
       <c r="AB37" s="8">
         <v>304</v>
       </c>
-      <c r="AC37" s="141" t="s">
+      <c r="AC37" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="AD37" s="142"/>
+      <c r="AD37" s="87"/>
     </row>
     <row r="38" spans="5:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E38" s="83" t="s">
+      <c r="E38" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="F38" s="88"/>
+      <c r="F38" s="71"/>
       <c r="G38" s="24" t="s">
         <v>33</v>
       </c>
@@ -3576,10 +3428,10 @@
         <v>46</v>
       </c>
       <c r="Q38"/>
-      <c r="S38" s="83" t="s">
+      <c r="S38" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="T38" s="88"/>
+      <c r="T38" s="71"/>
       <c r="U38" s="24" t="s">
         <v>33</v>
       </c>
@@ -3612,8 +3464,8 @@
       </c>
     </row>
     <row r="39" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E39" s="83"/>
-      <c r="F39" s="88"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="71"/>
       <c r="G39" s="23">
         <v>4</v>
       </c>
@@ -3647,8 +3499,8 @@
         <v>17.056856187290968</v>
       </c>
       <c r="Q39"/>
-      <c r="S39" s="83"/>
-      <c r="T39" s="88"/>
+      <c r="S39" s="70"/>
+      <c r="T39" s="71"/>
       <c r="U39" s="23">
         <v>4</v>
       </c>
@@ -3683,8 +3535,8 @@
       </c>
     </row>
     <row r="40" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E40" s="83"/>
-      <c r="F40" s="88"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="71"/>
       <c r="G40" s="23">
         <v>4</v>
       </c>
@@ -3718,8 +3570,8 @@
         <v>9.6440035016049013</v>
       </c>
       <c r="Q40"/>
-      <c r="S40" s="83"/>
-      <c r="T40" s="88"/>
+      <c r="S40" s="70"/>
+      <c r="T40" s="71"/>
       <c r="U40" s="23">
         <v>4</v>
       </c>
@@ -3754,8 +3606,8 @@
       </c>
     </row>
     <row r="41" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E41" s="83"/>
-      <c r="F41" s="88"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="71"/>
       <c r="G41" s="23">
         <v>4</v>
       </c>
@@ -3789,8 +3641,8 @@
         <v>9.1386861313868604</v>
       </c>
       <c r="Q41"/>
-      <c r="S41" s="83"/>
-      <c r="T41" s="88"/>
+      <c r="S41" s="70"/>
+      <c r="T41" s="71"/>
       <c r="U41" s="23">
         <v>4</v>
       </c>
@@ -3825,8 +3677,8 @@
       </c>
     </row>
     <row r="42" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E42" s="83"/>
-      <c r="F42" s="88"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="71"/>
       <c r="G42" s="23">
         <v>4</v>
       </c>
@@ -3859,8 +3711,8 @@
         <f t="shared" si="1"/>
         <v>0.54248248607867799</v>
       </c>
-      <c r="S42" s="83"/>
-      <c r="T42" s="88"/>
+      <c r="S42" s="70"/>
+      <c r="T42" s="71"/>
       <c r="U42" s="23">
         <v>4</v>
       </c>
@@ -3895,8 +3747,8 @@
       </c>
     </row>
     <row r="43" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E43" s="83"/>
-      <c r="F43" s="88"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="71"/>
       <c r="G43" s="23">
         <v>8</v>
       </c>
@@ -3929,8 +3781,8 @@
         <f t="shared" si="1"/>
         <v>0.28200185621474977</v>
       </c>
-      <c r="S43" s="83"/>
-      <c r="T43" s="88"/>
+      <c r="S43" s="70"/>
+      <c r="T43" s="71"/>
       <c r="U43" s="23">
         <v>8</v>
       </c>
@@ -3965,8 +3817,8 @@
       </c>
     </row>
     <row r="44" spans="5:31" x14ac:dyDescent="0.3">
-      <c r="E44" s="83"/>
-      <c r="F44" s="88"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="71"/>
       <c r="G44" s="23">
         <v>8</v>
       </c>
@@ -3999,8 +3851,8 @@
         <f t="shared" si="1"/>
         <v>-5.6277056277056277</v>
       </c>
-      <c r="S44" s="83"/>
-      <c r="T44" s="88"/>
+      <c r="S44" s="70"/>
+      <c r="T44" s="71"/>
       <c r="U44" s="23">
         <v>8</v>
       </c>
@@ -4035,8 +3887,8 @@
       </c>
     </row>
     <row r="45" spans="5:31" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E45" s="85"/>
-      <c r="F45" s="89"/>
+      <c r="E45" s="72"/>
+      <c r="F45" s="73"/>
       <c r="G45" s="25">
         <v>12</v>
       </c>
@@ -4069,8 +3921,8 @@
         <f t="shared" si="1"/>
         <v>-61.256930870796602</v>
       </c>
-      <c r="S45" s="85"/>
-      <c r="T45" s="89"/>
+      <c r="S45" s="72"/>
+      <c r="T45" s="73"/>
       <c r="U45" s="25">
         <v>12</v>
       </c>
@@ -4106,97 +3958,97 @@
     </row>
     <row r="47" spans="5:31" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="48" spans="5:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E48" s="90" t="s">
+      <c r="E48" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="F48" s="91"/>
-      <c r="G48" s="91"/>
-      <c r="H48" s="91"/>
-      <c r="I48" s="91"/>
-      <c r="J48" s="91"/>
-      <c r="K48" s="92"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="89"/>
+      <c r="I48" s="89"/>
+      <c r="J48" s="89"/>
+      <c r="K48" s="90"/>
       <c r="L48"/>
       <c r="M48"/>
-      <c r="N48" s="90" t="s">
+      <c r="N48" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="O48" s="91"/>
-      <c r="P48" s="91"/>
-      <c r="Q48" s="91"/>
-      <c r="R48" s="91"/>
-      <c r="S48" s="91"/>
-      <c r="T48" s="92"/>
-      <c r="W48" s="99" t="s">
+      <c r="O48" s="89"/>
+      <c r="P48" s="89"/>
+      <c r="Q48" s="89"/>
+      <c r="R48" s="89"/>
+      <c r="S48" s="89"/>
+      <c r="T48" s="90"/>
+      <c r="W48" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="X48" s="100"/>
-      <c r="Y48" s="100"/>
-      <c r="Z48" s="100"/>
-      <c r="AA48" s="100"/>
-      <c r="AB48" s="100"/>
-      <c r="AC48" s="100"/>
-      <c r="AD48" s="100"/>
-      <c r="AE48" s="101"/>
-    </row>
-    <row r="49" spans="5:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E49" s="93"/>
-      <c r="F49" s="94"/>
-      <c r="G49" s="94"/>
-      <c r="H49" s="94"/>
-      <c r="I49" s="94"/>
-      <c r="J49" s="94"/>
-      <c r="K49" s="95"/>
+      <c r="X48" s="77"/>
+      <c r="Y48" s="77"/>
+      <c r="Z48" s="77"/>
+      <c r="AA48" s="77"/>
+      <c r="AB48" s="77"/>
+      <c r="AC48" s="77"/>
+      <c r="AD48" s="77"/>
+      <c r="AE48" s="78"/>
+    </row>
+    <row r="49" spans="5:52" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E49" s="91"/>
+      <c r="F49" s="92"/>
+      <c r="G49" s="92"/>
+      <c r="H49" s="92"/>
+      <c r="I49" s="92"/>
+      <c r="J49" s="92"/>
+      <c r="K49" s="93"/>
       <c r="L49"/>
       <c r="M49"/>
-      <c r="N49" s="93"/>
-      <c r="O49" s="94"/>
-      <c r="P49" s="94"/>
-      <c r="Q49" s="94"/>
-      <c r="R49" s="94"/>
-      <c r="S49" s="94"/>
-      <c r="T49" s="95"/>
-      <c r="W49" s="102"/>
-      <c r="X49" s="103"/>
-      <c r="Y49" s="103"/>
-      <c r="Z49" s="103"/>
-      <c r="AA49" s="103"/>
-      <c r="AB49" s="103"/>
-      <c r="AC49" s="103"/>
-      <c r="AD49" s="103"/>
-      <c r="AE49" s="104"/>
-    </row>
-    <row r="50" spans="5:41" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E50" s="110"/>
-      <c r="F50" s="111"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="111"/>
-      <c r="J50" s="111"/>
-      <c r="K50" s="112"/>
+      <c r="N49" s="91"/>
+      <c r="O49" s="92"/>
+      <c r="P49" s="92"/>
+      <c r="Q49" s="92"/>
+      <c r="R49" s="92"/>
+      <c r="S49" s="92"/>
+      <c r="T49" s="93"/>
+      <c r="W49" s="79"/>
+      <c r="X49" s="80"/>
+      <c r="Y49" s="80"/>
+      <c r="Z49" s="80"/>
+      <c r="AA49" s="80"/>
+      <c r="AB49" s="80"/>
+      <c r="AC49" s="80"/>
+      <c r="AD49" s="80"/>
+      <c r="AE49" s="81"/>
+    </row>
+    <row r="50" spans="5:52" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E50" s="94"/>
+      <c r="F50" s="95"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
+      <c r="I50" s="95"/>
+      <c r="J50" s="95"/>
+      <c r="K50" s="96"/>
       <c r="L50"/>
       <c r="M50"/>
-      <c r="N50" s="110"/>
-      <c r="O50" s="111"/>
-      <c r="P50" s="111"/>
-      <c r="Q50" s="111"/>
-      <c r="R50" s="111"/>
-      <c r="S50" s="111"/>
-      <c r="T50" s="112"/>
-      <c r="W50" s="105"/>
-      <c r="X50" s="106"/>
-      <c r="Y50" s="106"/>
-      <c r="Z50" s="106"/>
-      <c r="AA50" s="106"/>
-      <c r="AB50" s="106"/>
-      <c r="AC50" s="106"/>
-      <c r="AD50" s="106"/>
-      <c r="AE50" s="107"/>
-    </row>
-    <row r="51" spans="5:41" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E51" s="81" t="s">
+      <c r="N50" s="94"/>
+      <c r="O50" s="95"/>
+      <c r="P50" s="95"/>
+      <c r="Q50" s="95"/>
+      <c r="R50" s="95"/>
+      <c r="S50" s="95"/>
+      <c r="T50" s="96"/>
+      <c r="W50" s="82"/>
+      <c r="X50" s="83"/>
+      <c r="Y50" s="83"/>
+      <c r="Z50" s="83"/>
+      <c r="AA50" s="83"/>
+      <c r="AB50" s="83"/>
+      <c r="AC50" s="83"/>
+      <c r="AD50" s="83"/>
+      <c r="AE50" s="84"/>
+    </row>
+    <row r="51" spans="5:52" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E51" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="F51" s="87"/>
+      <c r="F51" s="69"/>
       <c r="G51" s="32" t="s">
         <v>33</v>
       </c>
@@ -4212,10 +4064,10 @@
       <c r="K51" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="N51" s="81" t="s">
+      <c r="N51" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="O51" s="87"/>
+      <c r="O51" s="69"/>
       <c r="P51" s="32" t="s">
         <v>33</v>
       </c>
@@ -4231,10 +4083,10 @@
       <c r="T51" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="W51" s="81" t="s">
+      <c r="W51" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="X51" s="87"/>
+      <c r="X51" s="69"/>
       <c r="Y51" s="32" t="s">
         <v>54</v>
       </c>
@@ -4257,9 +4109,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="5:41" x14ac:dyDescent="0.3">
-      <c r="E52" s="83"/>
-      <c r="F52" s="88"/>
+    <row r="52" spans="5:52" x14ac:dyDescent="0.3">
+      <c r="E52" s="70"/>
+      <c r="F52" s="71"/>
       <c r="G52" s="35">
         <v>2</v>
       </c>
@@ -4275,8 +4127,8 @@
       <c r="K52" s="28">
         <v>512</v>
       </c>
-      <c r="N52" s="83"/>
-      <c r="O52" s="88"/>
+      <c r="N52" s="70"/>
+      <c r="O52" s="71"/>
       <c r="P52" s="35">
         <v>2</v>
       </c>
@@ -4292,8 +4144,8 @@
       <c r="T52" s="28">
         <v>578</v>
       </c>
-      <c r="W52" s="83"/>
-      <c r="X52" s="88"/>
+      <c r="W52" s="70"/>
+      <c r="X52" s="71"/>
       <c r="Y52" s="35">
         <v>6</v>
       </c>
@@ -4316,9 +4168,9 @@
         <v>672</v>
       </c>
     </row>
-    <row r="53" spans="5:41" x14ac:dyDescent="0.3">
-      <c r="E53" s="83"/>
-      <c r="F53" s="88"/>
+    <row r="53" spans="5:52" x14ac:dyDescent="0.3">
+      <c r="E53" s="70"/>
+      <c r="F53" s="71"/>
       <c r="G53" s="4">
         <v>2</v>
       </c>
@@ -4334,8 +4186,8 @@
       <c r="K53" s="5">
         <v>489</v>
       </c>
-      <c r="N53" s="83"/>
-      <c r="O53" s="88"/>
+      <c r="N53" s="70"/>
+      <c r="O53" s="71"/>
       <c r="P53" s="4">
         <v>2</v>
       </c>
@@ -4351,8 +4203,8 @@
       <c r="T53" s="5">
         <v>587</v>
       </c>
-      <c r="W53" s="83"/>
-      <c r="X53" s="88"/>
+      <c r="W53" s="70"/>
+      <c r="X53" s="71"/>
       <c r="Y53" s="4">
         <v>6</v>
       </c>
@@ -4375,9 +4227,9 @@
         <v>669</v>
       </c>
     </row>
-    <row r="54" spans="5:41" x14ac:dyDescent="0.3">
-      <c r="E54" s="83"/>
-      <c r="F54" s="88"/>
+    <row r="54" spans="5:52" x14ac:dyDescent="0.3">
+      <c r="E54" s="70"/>
+      <c r="F54" s="71"/>
       <c r="G54" s="29">
         <v>4</v>
       </c>
@@ -4393,8 +4245,8 @@
       <c r="K54" s="5">
         <v>303</v>
       </c>
-      <c r="N54" s="83"/>
-      <c r="O54" s="88"/>
+      <c r="N54" s="70"/>
+      <c r="O54" s="71"/>
       <c r="P54" s="29">
         <v>4</v>
       </c>
@@ -4410,8 +4262,8 @@
       <c r="T54" s="5">
         <v>327</v>
       </c>
-      <c r="W54" s="83"/>
-      <c r="X54" s="88"/>
+      <c r="W54" s="70"/>
+      <c r="X54" s="71"/>
       <c r="Y54" s="29">
         <v>8</v>
       </c>
@@ -4434,9 +4286,9 @@
         <v>651</v>
       </c>
     </row>
-    <row r="55" spans="5:41" x14ac:dyDescent="0.3">
-      <c r="E55" s="83"/>
-      <c r="F55" s="88"/>
+    <row r="55" spans="5:52" x14ac:dyDescent="0.3">
+      <c r="E55" s="70"/>
+      <c r="F55" s="71"/>
       <c r="G55" s="29">
         <v>4</v>
       </c>
@@ -4452,8 +4304,8 @@
       <c r="K55" s="5">
         <v>300</v>
       </c>
-      <c r="N55" s="83"/>
-      <c r="O55" s="88"/>
+      <c r="N55" s="70"/>
+      <c r="O55" s="71"/>
       <c r="P55" s="29">
         <v>4</v>
       </c>
@@ -4469,8 +4321,8 @@
       <c r="T55" s="5">
         <v>314</v>
       </c>
-      <c r="W55" s="83"/>
-      <c r="X55" s="88"/>
+      <c r="W55" s="70"/>
+      <c r="X55" s="71"/>
       <c r="Y55" s="29">
         <v>8</v>
       </c>
@@ -4493,9 +4345,9 @@
         <v>628</v>
       </c>
     </row>
-    <row r="56" spans="5:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="83"/>
-      <c r="F56" s="88"/>
+    <row r="56" spans="5:52" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E56" s="70"/>
+      <c r="F56" s="71"/>
       <c r="G56" s="29">
         <v>8</v>
       </c>
@@ -4511,8 +4363,8 @@
       <c r="K56" s="5">
         <v>329</v>
       </c>
-      <c r="N56" s="83"/>
-      <c r="O56" s="88"/>
+      <c r="N56" s="70"/>
+      <c r="O56" s="71"/>
       <c r="P56" s="29">
         <v>8</v>
       </c>
@@ -4528,8 +4380,8 @@
       <c r="T56" s="5">
         <v>543</v>
       </c>
-      <c r="W56" s="85"/>
-      <c r="X56" s="89"/>
+      <c r="W56" s="72"/>
+      <c r="X56" s="73"/>
       <c r="Y56" s="30">
         <v>8</v>
       </c>
@@ -4552,9 +4404,9 @@
         <v>313</v>
       </c>
     </row>
-    <row r="57" spans="5:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="85"/>
-      <c r="F57" s="89"/>
+    <row r="57" spans="5:52" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="72"/>
+      <c r="F57" s="73"/>
       <c r="G57" s="30">
         <v>8</v>
       </c>
@@ -4570,8 +4422,8 @@
       <c r="K57" s="8">
         <v>329</v>
       </c>
-      <c r="N57" s="85"/>
-      <c r="O57" s="89"/>
+      <c r="N57" s="72"/>
+      <c r="O57" s="73"/>
       <c r="P57" s="30">
         <v>8</v>
       </c>
@@ -4597,11 +4449,11 @@
       <c r="AD57"/>
       <c r="AE57"/>
     </row>
-    <row r="58" spans="5:41" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E58" s="81" t="s">
+    <row r="58" spans="5:52" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E58" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="F58" s="87"/>
+      <c r="F58" s="69"/>
       <c r="G58" s="32" t="s">
         <v>33</v>
       </c>
@@ -4617,10 +4469,10 @@
       <c r="K58" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="N58" s="81" t="s">
+      <c r="N58" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="O58" s="87"/>
+      <c r="O58" s="69"/>
       <c r="P58" s="32" t="s">
         <v>33</v>
       </c>
@@ -4637,9 +4489,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="5:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E59" s="83"/>
-      <c r="F59" s="88"/>
+    <row r="59" spans="5:52" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E59" s="70"/>
+      <c r="F59" s="71"/>
       <c r="G59" s="21">
         <v>2</v>
       </c>
@@ -4655,8 +4507,8 @@
       <c r="K59" s="22">
         <v>492</v>
       </c>
-      <c r="N59" s="83"/>
-      <c r="O59" s="88"/>
+      <c r="N59" s="70"/>
+      <c r="O59" s="71"/>
       <c r="P59" s="35">
         <v>2</v>
       </c>
@@ -4673,9 +4525,9 @@
         <v>629</v>
       </c>
     </row>
-    <row r="60" spans="5:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E60" s="83"/>
-      <c r="F60" s="88"/>
+    <row r="60" spans="5:52" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E60" s="70"/>
+      <c r="F60" s="71"/>
       <c r="G60" s="4">
         <v>2</v>
       </c>
@@ -4691,8 +4543,8 @@
       <c r="K60" s="5">
         <v>489</v>
       </c>
-      <c r="N60" s="83"/>
-      <c r="O60" s="88"/>
+      <c r="N60" s="70"/>
+      <c r="O60" s="71"/>
       <c r="P60" s="4">
         <v>2</v>
       </c>
@@ -4708,32 +4560,30 @@
       <c r="T60" s="5">
         <v>605</v>
       </c>
-      <c r="W60" s="99" t="s">
+      <c r="W60" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="X60" s="100"/>
-      <c r="Y60" s="100"/>
-      <c r="Z60" s="100"/>
-      <c r="AA60" s="100"/>
-      <c r="AB60" s="100"/>
-      <c r="AC60" s="101"/>
+      <c r="X60" s="77"/>
+      <c r="Y60" s="77"/>
+      <c r="Z60" s="77"/>
+      <c r="AA60" s="77"/>
+      <c r="AB60" s="77"/>
+      <c r="AC60" s="78"/>
       <c r="AD60"/>
       <c r="AE60"/>
-      <c r="AG60" s="99" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH60" s="100"/>
-      <c r="AI60" s="100"/>
-      <c r="AJ60" s="100"/>
-      <c r="AK60" s="100"/>
-      <c r="AL60" s="100"/>
-      <c r="AM60" s="101"/>
+      <c r="AG60"/>
+      <c r="AH60"/>
+      <c r="AI60"/>
+      <c r="AJ60"/>
+      <c r="AK60"/>
+      <c r="AL60"/>
+      <c r="AM60"/>
       <c r="AN60"/>
       <c r="AO60"/>
     </row>
-    <row r="61" spans="5:41" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E61" s="83"/>
-      <c r="F61" s="88"/>
+    <row r="61" spans="5:52" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E61" s="70"/>
+      <c r="F61" s="71"/>
       <c r="G61" s="31">
         <v>4</v>
       </c>
@@ -4749,8 +4599,8 @@
       <c r="K61" s="28">
         <v>307</v>
       </c>
-      <c r="N61" s="83"/>
-      <c r="O61" s="88"/>
+      <c r="N61" s="70"/>
+      <c r="O61" s="71"/>
       <c r="P61" s="29">
         <v>4</v>
       </c>
@@ -4766,28 +4616,28 @@
       <c r="T61" s="5">
         <v>322</v>
       </c>
-      <c r="W61" s="102"/>
-      <c r="X61" s="103"/>
-      <c r="Y61" s="103"/>
-      <c r="Z61" s="103"/>
-      <c r="AA61" s="103"/>
-      <c r="AB61" s="103"/>
-      <c r="AC61" s="104"/>
+      <c r="W61" s="79"/>
+      <c r="X61" s="80"/>
+      <c r="Y61" s="80"/>
+      <c r="Z61" s="80"/>
+      <c r="AA61" s="80"/>
+      <c r="AB61" s="80"/>
+      <c r="AC61" s="81"/>
       <c r="AD61"/>
       <c r="AE61"/>
-      <c r="AG61" s="102"/>
-      <c r="AH61" s="103"/>
-      <c r="AI61" s="103"/>
-      <c r="AJ61" s="103"/>
-      <c r="AK61" s="103"/>
-      <c r="AL61" s="103"/>
-      <c r="AM61" s="104"/>
+      <c r="AG61"/>
+      <c r="AH61"/>
+      <c r="AI61"/>
+      <c r="AJ61"/>
+      <c r="AK61"/>
+      <c r="AL61"/>
+      <c r="AM61"/>
       <c r="AN61"/>
       <c r="AO61"/>
     </row>
-    <row r="62" spans="5:41" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E62" s="83"/>
-      <c r="F62" s="88"/>
+    <row r="62" spans="5:52" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E62" s="70"/>
+      <c r="F62" s="71"/>
       <c r="G62" s="29">
         <v>4</v>
       </c>
@@ -4803,8 +4653,8 @@
       <c r="K62" s="5">
         <v>298</v>
       </c>
-      <c r="N62" s="83"/>
-      <c r="O62" s="88"/>
+      <c r="N62" s="70"/>
+      <c r="O62" s="71"/>
       <c r="P62" s="29">
         <v>4</v>
       </c>
@@ -4820,28 +4670,28 @@
       <c r="T62" s="5">
         <v>318</v>
       </c>
-      <c r="W62" s="105"/>
-      <c r="X62" s="106"/>
-      <c r="Y62" s="106"/>
-      <c r="Z62" s="106"/>
-      <c r="AA62" s="106"/>
-      <c r="AB62" s="106"/>
-      <c r="AC62" s="107"/>
+      <c r="W62" s="82"/>
+      <c r="X62" s="83"/>
+      <c r="Y62" s="83"/>
+      <c r="Z62" s="83"/>
+      <c r="AA62" s="83"/>
+      <c r="AB62" s="83"/>
+      <c r="AC62" s="84"/>
       <c r="AD62"/>
       <c r="AE62"/>
-      <c r="AG62" s="102"/>
-      <c r="AH62" s="103"/>
-      <c r="AI62" s="106"/>
-      <c r="AJ62" s="106"/>
-      <c r="AK62" s="106"/>
-      <c r="AL62" s="106"/>
-      <c r="AM62" s="107"/>
+      <c r="AG62"/>
+      <c r="AH62"/>
+      <c r="AI62"/>
+      <c r="AJ62"/>
+      <c r="AK62"/>
+      <c r="AL62"/>
+      <c r="AM62"/>
       <c r="AN62"/>
       <c r="AO62"/>
     </row>
-    <row r="63" spans="5:41" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E63" s="83"/>
-      <c r="F63" s="88"/>
+    <row r="63" spans="5:52" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E63" s="70"/>
+      <c r="F63" s="71"/>
       <c r="G63" s="29">
         <v>8</v>
       </c>
@@ -4857,8 +4707,8 @@
       <c r="K63" s="5">
         <v>357</v>
       </c>
-      <c r="N63" s="83"/>
-      <c r="O63" s="88"/>
+      <c r="N63" s="70"/>
+      <c r="O63" s="71"/>
       <c r="P63" s="29">
         <v>8</v>
       </c>
@@ -4874,10 +4724,10 @@
       <c r="T63" s="5">
         <v>510</v>
       </c>
-      <c r="W63" s="81" t="s">
+      <c r="W63" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="X63" s="82"/>
+      <c r="X63" s="85"/>
       <c r="Y63" s="32" t="s">
         <v>33</v>
       </c>
@@ -4893,29 +4743,30 @@
       <c r="AC63" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="AG63" s="143" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH63" s="144"/>
-      <c r="AI63" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ63" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK63" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL63" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM63" s="34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="5:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E64" s="85"/>
-      <c r="F64" s="89"/>
+      <c r="AG63"/>
+      <c r="AH63"/>
+      <c r="AI63"/>
+      <c r="AJ63"/>
+      <c r="AK63"/>
+      <c r="AL63"/>
+      <c r="AM63"/>
+      <c r="AN63"/>
+      <c r="AO63"/>
+      <c r="AP63"/>
+      <c r="AQ63"/>
+      <c r="AR63"/>
+      <c r="AS63"/>
+      <c r="AT63"/>
+      <c r="AU63"/>
+      <c r="AV63"/>
+      <c r="AW63"/>
+      <c r="AX63"/>
+      <c r="AY63"/>
+      <c r="AZ63"/>
+    </row>
+    <row r="64" spans="5:52" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E64" s="72"/>
+      <c r="F64" s="73"/>
       <c r="G64" s="30">
         <v>8</v>
       </c>
@@ -4931,8 +4782,8 @@
       <c r="K64" s="8">
         <v>341</v>
       </c>
-      <c r="N64" s="85"/>
-      <c r="O64" s="89"/>
+      <c r="N64" s="72"/>
+      <c r="O64" s="73"/>
       <c r="P64" s="30">
         <v>8</v>
       </c>
@@ -4948,8 +4799,8 @@
       <c r="T64" s="8">
         <v>409</v>
       </c>
-      <c r="W64" s="83"/>
-      <c r="X64" s="84"/>
+      <c r="W64" s="70"/>
+      <c r="X64" s="74"/>
       <c r="Y64" s="21">
         <v>2</v>
       </c>
@@ -4965,27 +4816,30 @@
       <c r="AC64" s="22">
         <v>25</v>
       </c>
-      <c r="AG64" s="145"/>
-      <c r="AH64" s="134"/>
-      <c r="AI64" s="21">
-        <v>2</v>
-      </c>
-      <c r="AJ64" s="20">
-        <v>62764</v>
-      </c>
-      <c r="AK64" s="20">
-        <v>59682</v>
-      </c>
-      <c r="AL64" s="37">
-        <v>331</v>
-      </c>
-      <c r="AM64" s="22">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W65" s="83"/>
-      <c r="X65" s="84"/>
+      <c r="AG64"/>
+      <c r="AH64"/>
+      <c r="AI64"/>
+      <c r="AJ64"/>
+      <c r="AK64"/>
+      <c r="AL64"/>
+      <c r="AM64"/>
+      <c r="AN64"/>
+      <c r="AO64"/>
+      <c r="AP64"/>
+      <c r="AQ64"/>
+      <c r="AR64"/>
+      <c r="AS64"/>
+      <c r="AT64"/>
+      <c r="AU64"/>
+      <c r="AV64"/>
+      <c r="AW64"/>
+      <c r="AX64"/>
+      <c r="AY64"/>
+      <c r="AZ64"/>
+    </row>
+    <row r="65" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W65" s="70"/>
+      <c r="X65" s="74"/>
       <c r="Y65" s="4">
         <v>3</v>
       </c>
@@ -5001,27 +4855,30 @@
       <c r="AC65" s="5">
         <v>31</v>
       </c>
-      <c r="AG65" s="145"/>
-      <c r="AH65" s="134"/>
-      <c r="AI65" s="4">
-        <v>3</v>
-      </c>
-      <c r="AJ65" s="64">
-        <v>76297</v>
-      </c>
-      <c r="AK65" s="64">
-        <v>82110</v>
-      </c>
-      <c r="AL65" s="64">
-        <v>303</v>
-      </c>
-      <c r="AM65" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W66" s="83"/>
-      <c r="X66" s="84"/>
+      <c r="AG65"/>
+      <c r="AH65"/>
+      <c r="AI65"/>
+      <c r="AJ65"/>
+      <c r="AK65"/>
+      <c r="AL65"/>
+      <c r="AM65"/>
+      <c r="AN65"/>
+      <c r="AO65"/>
+      <c r="AP65"/>
+      <c r="AQ65"/>
+      <c r="AR65"/>
+      <c r="AS65"/>
+      <c r="AT65"/>
+      <c r="AU65"/>
+      <c r="AV65"/>
+      <c r="AW65"/>
+      <c r="AX65"/>
+      <c r="AY65"/>
+      <c r="AZ65"/>
+    </row>
+    <row r="66" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W66" s="70"/>
+      <c r="X66" s="74"/>
       <c r="Y66" s="4">
         <v>4</v>
       </c>
@@ -5038,28 +4895,30 @@
         <v>31</v>
       </c>
       <c r="AE66" s="46"/>
-      <c r="AG66" s="145"/>
-      <c r="AH66" s="134"/>
-      <c r="AI66" s="4">
-        <v>4</v>
-      </c>
-      <c r="AJ66" s="64">
-        <v>102637</v>
-      </c>
-      <c r="AK66" s="64">
-        <v>103139</v>
-      </c>
-      <c r="AL66" s="65">
-        <v>298</v>
-      </c>
-      <c r="AM66" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO66" s="46"/>
-    </row>
-    <row r="67" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W67" s="83"/>
-      <c r="X67" s="84"/>
+      <c r="AG66"/>
+      <c r="AH66"/>
+      <c r="AI66"/>
+      <c r="AJ66"/>
+      <c r="AK66"/>
+      <c r="AL66"/>
+      <c r="AM66"/>
+      <c r="AN66"/>
+      <c r="AO66"/>
+      <c r="AP66"/>
+      <c r="AQ66"/>
+      <c r="AR66"/>
+      <c r="AS66"/>
+      <c r="AT66"/>
+      <c r="AU66"/>
+      <c r="AV66"/>
+      <c r="AW66"/>
+      <c r="AX66"/>
+      <c r="AY66"/>
+      <c r="AZ66"/>
+    </row>
+    <row r="67" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W67" s="70"/>
+      <c r="X67" s="74"/>
       <c r="Y67" s="29">
         <v>5</v>
       </c>
@@ -5075,45 +4934,30 @@
       <c r="AC67" s="5">
         <v>40</v>
       </c>
-      <c r="AG67" s="145"/>
-      <c r="AH67" s="134"/>
-      <c r="AI67" s="29">
-        <v>5</v>
-      </c>
-      <c r="AJ67" s="64">
-        <v>157548</v>
-      </c>
-      <c r="AK67" s="64">
-        <v>168731</v>
-      </c>
-      <c r="AL67" s="65">
-        <v>310</v>
-      </c>
-      <c r="AM67" s="5">
-        <f>78-26</f>
-        <v>52</v>
-      </c>
+      <c r="AG67"/>
+      <c r="AH67"/>
+      <c r="AI67"/>
+      <c r="AJ67"/>
+      <c r="AK67"/>
+      <c r="AL67"/>
+      <c r="AM67"/>
+      <c r="AN67"/>
+      <c r="AO67"/>
+      <c r="AP67"/>
       <c r="AQ67"/>
       <c r="AR67"/>
-      <c r="AS67" s="39">
-        <v>8</v>
-      </c>
-      <c r="AT67" s="62">
-        <v>241577</v>
-      </c>
-      <c r="AU67" s="62">
-        <v>233152</v>
-      </c>
-      <c r="AV67" s="63">
-        <v>301</v>
-      </c>
-      <c r="AW67" s="42">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="68" spans="23:49" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W68" s="83"/>
-      <c r="X68" s="84"/>
+      <c r="AS67"/>
+      <c r="AT67"/>
+      <c r="AU67"/>
+      <c r="AV67"/>
+      <c r="AW67"/>
+      <c r="AX67"/>
+      <c r="AY67"/>
+      <c r="AZ67"/>
+    </row>
+    <row r="68" spans="23:52" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W68" s="70"/>
+      <c r="X68" s="74"/>
       <c r="Y68" s="39">
         <v>8</v>
       </c>
@@ -5129,27 +4973,30 @@
       <c r="AC68" s="42">
         <v>44</v>
       </c>
-      <c r="AG68" s="146"/>
-      <c r="AH68" s="147"/>
-      <c r="AI68" s="6">
-        <v>8</v>
-      </c>
-      <c r="AJ68" s="7">
-        <v>186808</v>
-      </c>
-      <c r="AK68" s="7">
-        <v>204566</v>
-      </c>
-      <c r="AL68" s="7">
-        <v>308</v>
-      </c>
-      <c r="AM68" s="8">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="23:49" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W69" s="85"/>
-      <c r="X69" s="86"/>
+      <c r="AG68"/>
+      <c r="AH68"/>
+      <c r="AI68"/>
+      <c r="AJ68"/>
+      <c r="AK68"/>
+      <c r="AL68"/>
+      <c r="AM68"/>
+      <c r="AN68"/>
+      <c r="AO68"/>
+      <c r="AP68"/>
+      <c r="AQ68"/>
+      <c r="AR68"/>
+      <c r="AS68"/>
+      <c r="AT68"/>
+      <c r="AU68"/>
+      <c r="AV68"/>
+      <c r="AW68"/>
+      <c r="AX68"/>
+      <c r="AY68"/>
+      <c r="AZ68"/>
+    </row>
+    <row r="69" spans="23:52" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W69" s="72"/>
+      <c r="X69" s="75"/>
       <c r="Y69" s="30">
         <v>16</v>
       </c>
@@ -5165,37 +5012,32 @@
       <c r="AC69" s="8">
         <v>44</v>
       </c>
-      <c r="AG69" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH69" s="88"/>
-      <c r="AI69" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ69" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK69" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL69" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM69" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="AN69" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO69" s="34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="70" spans="23:49" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W70" s="81" t="s">
+      <c r="AG69"/>
+      <c r="AH69"/>
+      <c r="AI69"/>
+      <c r="AJ69"/>
+      <c r="AK69"/>
+      <c r="AL69"/>
+      <c r="AM69"/>
+      <c r="AN69"/>
+      <c r="AO69"/>
+      <c r="AP69"/>
+      <c r="AQ69"/>
+      <c r="AR69"/>
+      <c r="AS69"/>
+      <c r="AT69"/>
+      <c r="AU69"/>
+      <c r="AV69"/>
+      <c r="AW69"/>
+      <c r="AX69"/>
+      <c r="AY69"/>
+      <c r="AZ69"/>
+    </row>
+    <row r="70" spans="23:52" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W70" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="X70" s="87"/>
+      <c r="X70" s="69"/>
       <c r="Y70" s="32" t="s">
         <v>33</v>
       </c>
@@ -5217,36 +5059,30 @@
       <c r="AE70" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="AG70" s="83"/>
-      <c r="AH70" s="84"/>
-      <c r="AI70" s="70">
-        <v>2</v>
-      </c>
-      <c r="AJ70" s="67">
-        <v>15702</v>
-      </c>
-      <c r="AK70" s="67">
-        <v>21154</v>
-      </c>
-      <c r="AL70" s="68">
-        <v>437</v>
-      </c>
-      <c r="AM70" s="69">
-        <f>AM64+26</f>
-        <v>60</v>
-      </c>
-      <c r="AN70" s="59">
-        <f t="shared" ref="AN70:AO74" si="4">(AJ70-AJ64)/AJ64*100</f>
-        <v>-74.982474029698551</v>
-      </c>
-      <c r="AO70" s="56">
-        <f t="shared" si="4"/>
-        <v>-64.555477363359131</v>
-      </c>
-    </row>
-    <row r="71" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W71" s="83"/>
-      <c r="X71" s="88"/>
+      <c r="AG70"/>
+      <c r="AH70"/>
+      <c r="AI70"/>
+      <c r="AJ70"/>
+      <c r="AK70"/>
+      <c r="AL70"/>
+      <c r="AM70"/>
+      <c r="AN70"/>
+      <c r="AO70"/>
+      <c r="AP70"/>
+      <c r="AQ70"/>
+      <c r="AR70"/>
+      <c r="AS70"/>
+      <c r="AT70"/>
+      <c r="AU70"/>
+      <c r="AV70"/>
+      <c r="AW70"/>
+      <c r="AX70"/>
+      <c r="AY70"/>
+      <c r="AZ70"/>
+    </row>
+    <row r="71" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W71" s="70"/>
+      <c r="X71" s="71"/>
       <c r="Y71" s="35">
         <v>2</v>
       </c>
@@ -5264,43 +5100,37 @@
         <v>29</v>
       </c>
       <c r="AD71" s="59">
-        <f t="shared" ref="AD71:AE76" si="5">(Z71-Z64)/Z64*100</f>
+        <f t="shared" ref="AD71:AE76" si="4">(Z71-Z64)/Z64*100</f>
         <v>-37.870168536338987</v>
       </c>
       <c r="AE71" s="56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-13.875999329121708</v>
       </c>
-      <c r="AG71" s="83"/>
-      <c r="AH71" s="84"/>
-      <c r="AI71" s="4">
-        <v>3</v>
-      </c>
-      <c r="AJ71" s="64">
-        <v>18507</v>
-      </c>
-      <c r="AK71" s="64">
-        <v>27108</v>
-      </c>
-      <c r="AL71" s="64">
-        <v>311</v>
-      </c>
-      <c r="AM71" s="5">
-        <f t="shared" ref="AM71:AM74" si="6">AM65+26</f>
-        <v>66</v>
-      </c>
-      <c r="AN71" s="47">
-        <f t="shared" si="4"/>
-        <v>-75.743476152404426</v>
-      </c>
-      <c r="AO71" s="48">
-        <f t="shared" si="4"/>
-        <v>-66.985750822067956</v>
-      </c>
-    </row>
-    <row r="72" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W72" s="83"/>
-      <c r="X72" s="88"/>
+      <c r="AG71"/>
+      <c r="AH71"/>
+      <c r="AI71"/>
+      <c r="AJ71"/>
+      <c r="AK71"/>
+      <c r="AL71"/>
+      <c r="AM71"/>
+      <c r="AN71"/>
+      <c r="AO71"/>
+      <c r="AP71"/>
+      <c r="AQ71"/>
+      <c r="AR71"/>
+      <c r="AS71"/>
+      <c r="AT71"/>
+      <c r="AU71"/>
+      <c r="AV71"/>
+      <c r="AW71"/>
+      <c r="AX71"/>
+      <c r="AY71"/>
+      <c r="AZ71"/>
+    </row>
+    <row r="72" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W72" s="70"/>
+      <c r="X72" s="71"/>
       <c r="Y72" s="4">
         <v>3</v>
       </c>
@@ -5314,47 +5144,30 @@
         <v>319</v>
       </c>
       <c r="AC72" s="36">
-        <f t="shared" ref="AC72:AC76" si="7">AC65+4</f>
+        <f t="shared" ref="AC72:AC76" si="5">AC65+4</f>
         <v>35</v>
       </c>
       <c r="AD72" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-30.858359957401493</v>
       </c>
       <c r="AE72" s="48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-32.457433584829296</v>
       </c>
-      <c r="AG72" s="83"/>
-      <c r="AH72" s="84"/>
-      <c r="AI72" s="4">
-        <v>4</v>
-      </c>
-      <c r="AJ72" s="64">
-        <v>23088</v>
-      </c>
-      <c r="AK72" s="64">
-        <v>33154</v>
-      </c>
-      <c r="AL72" s="64">
-        <v>305</v>
-      </c>
-      <c r="AM72" s="5">
-        <f t="shared" si="6"/>
-        <v>66</v>
-      </c>
-      <c r="AN72" s="47">
-        <f t="shared" si="4"/>
-        <v>-77.505188187495733</v>
-      </c>
-      <c r="AO72" s="48">
-        <f t="shared" si="4"/>
-        <v>-67.855030589786608</v>
-      </c>
-    </row>
-    <row r="73" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W73" s="83"/>
-      <c r="X73" s="88"/>
+      <c r="AG72"/>
+      <c r="AH72"/>
+      <c r="AI72"/>
+      <c r="AJ72"/>
+      <c r="AK72"/>
+      <c r="AL72"/>
+      <c r="AM72"/>
+      <c r="AN72"/>
+      <c r="AO72"/>
+    </row>
+    <row r="73" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W73" s="70"/>
+      <c r="X73" s="71"/>
       <c r="Y73" s="4">
         <v>4</v>
       </c>
@@ -5368,47 +5181,30 @@
         <v>308</v>
       </c>
       <c r="AC73" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="AD73" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-24.89957172736629</v>
       </c>
       <c r="AE73" s="48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-25.368341055625017</v>
       </c>
-      <c r="AG73" s="83"/>
-      <c r="AH73" s="84"/>
-      <c r="AI73" s="29">
-        <v>5</v>
-      </c>
-      <c r="AJ73" s="2">
-        <v>30171</v>
-      </c>
-      <c r="AK73" s="2">
-        <v>41800</v>
-      </c>
-      <c r="AL73" s="2">
-        <v>297</v>
-      </c>
-      <c r="AM73" s="5">
-        <f t="shared" si="6"/>
-        <v>78</v>
-      </c>
-      <c r="AN73" s="47">
-        <f t="shared" si="4"/>
-        <v>-80.849645822225597</v>
-      </c>
-      <c r="AO73" s="48">
-        <f t="shared" si="4"/>
-        <v>-75.226840355358533</v>
-      </c>
-    </row>
-    <row r="74" spans="23:49" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W74" s="83"/>
-      <c r="X74" s="88"/>
+      <c r="AG73"/>
+      <c r="AH73"/>
+      <c r="AI73"/>
+      <c r="AJ73"/>
+      <c r="AK73"/>
+      <c r="AL73"/>
+      <c r="AM73"/>
+      <c r="AN73"/>
+      <c r="AO73"/>
+    </row>
+    <row r="74" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W74" s="70"/>
+      <c r="X74" s="71"/>
       <c r="Y74" s="29">
         <v>5</v>
       </c>
@@ -5422,47 +5218,30 @@
         <v>394</v>
       </c>
       <c r="AC74" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
       <c r="AD74" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-24.903194578896418</v>
       </c>
       <c r="AE74" s="48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-26.444704142717452</v>
       </c>
-      <c r="AG74" s="85"/>
-      <c r="AH74" s="86"/>
-      <c r="AI74" s="6">
-        <v>8</v>
-      </c>
-      <c r="AJ74" s="7">
-        <v>36635</v>
-      </c>
-      <c r="AK74" s="7">
-        <v>48979</v>
-      </c>
-      <c r="AL74" s="7">
-        <v>309</v>
-      </c>
-      <c r="AM74" s="8">
-        <f t="shared" si="6"/>
-        <v>83</v>
-      </c>
-      <c r="AN74" s="60">
-        <f t="shared" si="4"/>
-        <v>-80.388955505117551</v>
-      </c>
-      <c r="AO74" s="55">
-        <f t="shared" si="4"/>
-        <v>-76.057116040788799</v>
-      </c>
-    </row>
-    <row r="75" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W75" s="83"/>
-      <c r="X75" s="88"/>
+      <c r="AG74"/>
+      <c r="AH74"/>
+      <c r="AI74"/>
+      <c r="AJ74"/>
+      <c r="AK74"/>
+      <c r="AL74"/>
+      <c r="AM74"/>
+      <c r="AN74"/>
+      <c r="AO74"/>
+    </row>
+    <row r="75" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W75" s="70"/>
+      <c r="X75" s="71"/>
       <c r="Y75" s="29">
         <v>8</v>
       </c>
@@ -5476,30 +5255,30 @@
         <v>373</v>
       </c>
       <c r="AC75" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="AD75" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-15.212906183735459</v>
       </c>
       <c r="AE75" s="48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-21.810127336657462</v>
       </c>
-      <c r="AG75" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH75" s="100"/>
-      <c r="AI75" s="103"/>
-      <c r="AJ75" s="103"/>
-      <c r="AK75" s="103"/>
-      <c r="AL75" s="103"/>
-      <c r="AM75" s="104"/>
-    </row>
-    <row r="76" spans="23:49" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W76" s="85"/>
-      <c r="X76" s="89"/>
+      <c r="AG75"/>
+      <c r="AH75"/>
+      <c r="AI75"/>
+      <c r="AJ75"/>
+      <c r="AK75"/>
+      <c r="AL75"/>
+      <c r="AM75"/>
+      <c r="AN75"/>
+      <c r="AO75"/>
+    </row>
+    <row r="76" spans="23:52" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W76" s="72"/>
+      <c r="X76" s="73"/>
       <c r="Y76" s="52">
         <v>16</v>
       </c>
@@ -5513,32 +5292,32 @@
         <v>358</v>
       </c>
       <c r="AC76" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="AD76" s="49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-9.0295121179077711</v>
       </c>
       <c r="AE76" s="50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-13.68932819029251</v>
       </c>
-      <c r="AG76" s="102"/>
-      <c r="AH76" s="103"/>
-      <c r="AI76" s="103"/>
-      <c r="AJ76" s="103"/>
-      <c r="AK76" s="103"/>
-      <c r="AL76" s="103"/>
-      <c r="AM76" s="104"/>
+      <c r="AG76"/>
+      <c r="AH76"/>
+      <c r="AI76"/>
+      <c r="AJ76"/>
+      <c r="AK76"/>
+      <c r="AL76"/>
+      <c r="AM76"/>
       <c r="AN76"/>
       <c r="AO76"/>
     </row>
-    <row r="77" spans="23:49" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W77" s="81" t="s">
-        <v>65</v>
-      </c>
-      <c r="X77" s="87"/>
+    <row r="77" spans="23:52" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W77" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="X77" s="69"/>
       <c r="Y77" s="32" t="s">
         <v>33</v>
       </c>
@@ -5560,19 +5339,19 @@
       <c r="AE77" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="AG77" s="102"/>
-      <c r="AH77" s="103"/>
-      <c r="AI77" s="106"/>
-      <c r="AJ77" s="106"/>
-      <c r="AK77" s="106"/>
-      <c r="AL77" s="106"/>
-      <c r="AM77" s="107"/>
+      <c r="AG77"/>
+      <c r="AH77"/>
+      <c r="AI77"/>
+      <c r="AJ77"/>
+      <c r="AK77"/>
+      <c r="AL77"/>
+      <c r="AM77"/>
       <c r="AN77"/>
       <c r="AO77"/>
     </row>
-    <row r="78" spans="23:49" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W78" s="83"/>
-      <c r="X78" s="88"/>
+    <row r="78" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W78" s="70"/>
+      <c r="X78" s="71"/>
       <c r="Y78" s="35">
         <v>2</v>
       </c>
@@ -5597,31 +5376,19 @@
         <f>(AA78-AA64)/AA64*100</f>
         <v>-55.872980376809977</v>
       </c>
-      <c r="AG78" s="143" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH78" s="144"/>
-      <c r="AI78" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ78" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK78" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL78" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM78" s="34" t="s">
-        <v>59</v>
-      </c>
+      <c r="AG78"/>
+      <c r="AH78"/>
+      <c r="AI78"/>
+      <c r="AJ78"/>
+      <c r="AK78"/>
+      <c r="AL78"/>
+      <c r="AM78"/>
       <c r="AN78"/>
       <c r="AO78"/>
     </row>
-    <row r="79" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W79" s="83"/>
-      <c r="X79" s="88"/>
+    <row r="79" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W79" s="70"/>
+      <c r="X79" s="71"/>
       <c r="Y79" s="4">
         <v>3</v>
       </c>
@@ -5635,38 +5402,30 @@
         <v>321</v>
       </c>
       <c r="AC79" s="36">
-        <f t="shared" ref="AC79:AC83" si="8">AC65+17</f>
+        <f t="shared" ref="AC79:AC83" si="6">AC65+17</f>
         <v>48</v>
       </c>
       <c r="AD79" s="47">
-        <f t="shared" ref="AD79:AD81" si="9">-(Z65-Z79)/Z65*100</f>
+        <f t="shared" ref="AD79:AD81" si="7">-(Z65-Z79)/Z65*100</f>
         <v>-71.09691160809372</v>
       </c>
       <c r="AE79" s="48">
-        <f t="shared" ref="AE79:AE81" si="10">(AA79-AA65)/AA65*100</f>
+        <f t="shared" ref="AE79:AE81" si="8">(AA79-AA65)/AA65*100</f>
         <v>-69.060214494261842</v>
       </c>
-      <c r="AG79" s="145"/>
-      <c r="AH79" s="134"/>
-      <c r="AI79" s="21">
-        <v>2</v>
-      </c>
-      <c r="AJ79" s="20">
-        <v>141432</v>
-      </c>
-      <c r="AK79" s="20">
-        <v>141913</v>
-      </c>
-      <c r="AL79" s="37">
-        <v>306</v>
-      </c>
-      <c r="AM79" s="22">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" spans="23:49" x14ac:dyDescent="0.3">
-      <c r="W80" s="83"/>
-      <c r="X80" s="88"/>
+      <c r="AG79"/>
+      <c r="AH79"/>
+      <c r="AI79"/>
+      <c r="AJ79"/>
+      <c r="AK79"/>
+      <c r="AL79"/>
+      <c r="AM79"/>
+      <c r="AN79"/>
+      <c r="AO79"/>
+    </row>
+    <row r="80" spans="23:52" x14ac:dyDescent="0.3">
+      <c r="W80" s="70"/>
+      <c r="X80" s="71"/>
       <c r="Y80" s="4">
         <v>4</v>
       </c>
@@ -5680,38 +5439,30 @@
         <v>325</v>
       </c>
       <c r="AC80" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="AD80" s="47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>-71.54808937286279</v>
       </c>
       <c r="AE80" s="48">
         <f>(AA80-AA66)/AA66*100</f>
         <v>-67.730626853962889</v>
       </c>
-      <c r="AG80" s="145"/>
-      <c r="AH80" s="134"/>
-      <c r="AI80" s="4">
-        <v>3</v>
-      </c>
-      <c r="AJ80" s="2">
-        <v>227005</v>
-      </c>
-      <c r="AK80" s="2">
-        <v>245202</v>
-      </c>
-      <c r="AL80" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM80" s="5">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="81" spans="23:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W81" s="83"/>
-      <c r="X81" s="88"/>
+      <c r="AG80"/>
+      <c r="AH80"/>
+      <c r="AI80"/>
+      <c r="AJ80"/>
+      <c r="AK80"/>
+      <c r="AL80"/>
+      <c r="AM80"/>
+      <c r="AN80"/>
+      <c r="AO80"/>
+    </row>
+    <row r="81" spans="23:41" x14ac:dyDescent="0.3">
+      <c r="W81" s="70"/>
+      <c r="X81" s="71"/>
       <c r="Y81" s="29">
         <v>5</v>
       </c>
@@ -5725,38 +5476,30 @@
         <v>427</v>
       </c>
       <c r="AC81" s="36">
+        <f t="shared" si="6"/>
+        <v>57</v>
+      </c>
+      <c r="AD81" s="47">
+        <f t="shared" si="7"/>
+        <v>-66.086986585534504</v>
+      </c>
+      <c r="AE81" s="48">
         <f t="shared" si="8"/>
-        <v>57</v>
-      </c>
-      <c r="AD81" s="47">
-        <f t="shared" si="9"/>
-        <v>-66.086986585534504</v>
-      </c>
-      <c r="AE81" s="48">
-        <f t="shared" si="10"/>
         <v>-65.358105368599297</v>
       </c>
-      <c r="AG81" s="146"/>
-      <c r="AH81" s="147"/>
-      <c r="AI81" s="39">
-        <v>4</v>
-      </c>
-      <c r="AJ81" s="40">
-        <v>311939</v>
-      </c>
-      <c r="AK81" s="40">
-        <v>315405</v>
-      </c>
-      <c r="AL81" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM81" s="42">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="82" spans="23:41" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W82" s="83"/>
-      <c r="X82" s="88"/>
+      <c r="AG81"/>
+      <c r="AH81"/>
+      <c r="AI81"/>
+      <c r="AJ81"/>
+      <c r="AK81"/>
+      <c r="AL81"/>
+      <c r="AM81"/>
+      <c r="AN81"/>
+      <c r="AO81"/>
+    </row>
+    <row r="82" spans="23:41" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W82" s="70"/>
+      <c r="X82" s="71"/>
       <c r="Y82" s="29">
         <v>8</v>
       </c>
@@ -5770,7 +5513,7 @@
         <v>422</v>
       </c>
       <c r="AC82" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>61</v>
       </c>
       <c r="AD82" s="47">
@@ -5781,35 +5524,19 @@
         <f>(AA82-AA68)/AA68*100</f>
         <v>-63.783547547627087</v>
       </c>
-      <c r="AG82" s="81" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH82" s="87"/>
-      <c r="AI82" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ82" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK82" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL82" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM82" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="AN82" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO82" s="22" t="s">
-        <v>46</v>
-      </c>
+      <c r="AG82"/>
+      <c r="AH82"/>
+      <c r="AI82"/>
+      <c r="AJ82"/>
+      <c r="AK82"/>
+      <c r="AL82"/>
+      <c r="AM82"/>
+      <c r="AN82"/>
+      <c r="AO82"/>
     </row>
     <row r="83" spans="23:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W83" s="85"/>
-      <c r="X83" s="89"/>
+      <c r="W83" s="72"/>
+      <c r="X83" s="73"/>
       <c r="Y83" s="43">
         <v>16</v>
       </c>
@@ -5823,7 +5550,7 @@
         <v>361</v>
       </c>
       <c r="AC83" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>61</v>
       </c>
       <c r="AD83" s="60">
@@ -5834,37 +5561,21 @@
         <f>(AA83-AA69)/AA69*100</f>
         <v>-57.409193185470912</v>
       </c>
-      <c r="AG83" s="83"/>
-      <c r="AH83" s="88"/>
-      <c r="AI83" s="21">
-        <v>2</v>
-      </c>
-      <c r="AJ83" s="20">
-        <v>33202</v>
-      </c>
-      <c r="AK83" s="20">
-        <v>99066</v>
-      </c>
-      <c r="AL83" s="37">
-        <v>351</v>
-      </c>
-      <c r="AM83" s="22">
-        <v>132</v>
-      </c>
-      <c r="AN83" s="47">
-        <f>(AJ83-AJ79)/AJ79*100</f>
-        <v>-76.524407489111383</v>
-      </c>
-      <c r="AO83" s="48">
-        <f>(AK83-AK79)/AK79*100</f>
-        <v>-30.192441848174585</v>
-      </c>
+      <c r="AG83"/>
+      <c r="AH83"/>
+      <c r="AI83"/>
+      <c r="AJ83"/>
+      <c r="AK83"/>
+      <c r="AL83"/>
+      <c r="AM83"/>
+      <c r="AN83"/>
+      <c r="AO83"/>
     </row>
     <row r="84" spans="23:41" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W84" s="81" t="s">
-        <v>66</v>
-      </c>
-      <c r="X84" s="87"/>
+      <c r="W84" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="X84" s="69"/>
       <c r="Y84" s="32" t="s">
         <v>33</v>
       </c>
@@ -5886,35 +5597,19 @@
       <c r="AE84" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="AG84" s="83"/>
-      <c r="AH84" s="88"/>
-      <c r="AI84" s="4">
-        <v>3</v>
-      </c>
-      <c r="AJ84" s="2">
-        <v>44398</v>
-      </c>
-      <c r="AK84" s="2">
-        <v>133626</v>
-      </c>
-      <c r="AL84" s="2">
-        <v>305</v>
-      </c>
-      <c r="AM84" s="5">
-        <v>144</v>
-      </c>
-      <c r="AN84" s="47">
-        <f>(AJ84-AJ80)/AJ80*100</f>
-        <v>-80.441840488094968</v>
-      </c>
-      <c r="AO84" s="48">
-        <f t="shared" ref="AN84:AO85" si="11">(AK84-AK80)/AK80*100</f>
-        <v>-45.503707147576286</v>
-      </c>
-    </row>
-    <row r="85" spans="23:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W85" s="83"/>
-      <c r="X85" s="88"/>
+      <c r="AG84"/>
+      <c r="AH84"/>
+      <c r="AI84"/>
+      <c r="AJ84"/>
+      <c r="AK84"/>
+      <c r="AL84"/>
+      <c r="AM84"/>
+      <c r="AN84"/>
+      <c r="AO84"/>
+    </row>
+    <row r="85" spans="23:41" x14ac:dyDescent="0.3">
+      <c r="W85" s="70"/>
+      <c r="X85" s="71"/>
       <c r="Y85" s="35">
         <v>2</v>
       </c>
@@ -5938,35 +5633,19 @@
         <f>(AA85-AA64)/AA64*100</f>
         <v>-59.719349248057249</v>
       </c>
-      <c r="AG85" s="85"/>
-      <c r="AH85" s="89"/>
-      <c r="AI85" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ85" s="7">
-        <v>58104</v>
-      </c>
-      <c r="AK85" s="7">
-        <v>162790</v>
-      </c>
-      <c r="AL85" s="58">
-        <v>298</v>
-      </c>
-      <c r="AM85" s="8">
-        <v>144</v>
-      </c>
-      <c r="AN85" s="47">
-        <f t="shared" si="11"/>
-        <v>-81.373281314615994</v>
-      </c>
-      <c r="AO85" s="48">
-        <f t="shared" si="11"/>
-        <v>-48.38699449913603</v>
-      </c>
+      <c r="AG85"/>
+      <c r="AH85"/>
+      <c r="AI85"/>
+      <c r="AJ85"/>
+      <c r="AK85"/>
+      <c r="AL85"/>
+      <c r="AM85"/>
+      <c r="AN85"/>
+      <c r="AO85"/>
     </row>
     <row r="86" spans="23:41" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W86" s="83"/>
-      <c r="X86" s="88"/>
+      <c r="W86" s="70"/>
+      <c r="X86" s="71"/>
       <c r="Y86" s="4">
         <v>3</v>
       </c>
@@ -5981,19 +5660,19 @@
       </c>
       <c r="AC86" s="36"/>
       <c r="AD86" s="59">
-        <f t="shared" ref="AD86:AD89" si="12">-(Z65-Z86)/Z65*100</f>
+        <f t="shared" ref="AD86:AD89" si="9">-(Z65-Z86)/Z65*100</f>
         <v>-73.91693290734824</v>
       </c>
       <c r="AE86" s="56">
-        <f t="shared" ref="AE86:AE89" si="13">(AA86-AA65)/AA65*100</f>
+        <f t="shared" ref="AE86:AE89" si="10">(AA86-AA65)/AA65*100</f>
         <v>-72.251611597722089</v>
       </c>
       <c r="AG86" s="61"/>
       <c r="AH86" s="61"/>
     </row>
-    <row r="87" spans="23:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W87" s="83"/>
-      <c r="X87" s="88"/>
+    <row r="87" spans="23:41" x14ac:dyDescent="0.3">
+      <c r="W87" s="70"/>
+      <c r="X87" s="71"/>
       <c r="Y87" s="4">
         <v>4</v>
       </c>
@@ -6008,19 +5687,19 @@
       </c>
       <c r="AC87" s="36"/>
       <c r="AD87" s="59">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>-74.804953354802294</v>
       </c>
       <c r="AE87" s="56">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>-71.175014096246727</v>
       </c>
       <c r="AG87" s="61"/>
       <c r="AH87" s="61"/>
     </row>
     <row r="88" spans="23:41" x14ac:dyDescent="0.3">
-      <c r="W88" s="83"/>
-      <c r="X88" s="88"/>
+      <c r="W88" s="70"/>
+      <c r="X88" s="71"/>
       <c r="Y88" s="29">
         <v>5</v>
       </c>
@@ -6035,26 +5714,26 @@
       </c>
       <c r="AC88" s="36"/>
       <c r="AD88" s="59">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>-71.380168718019647</v>
       </c>
       <c r="AE88" s="56">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>-69.961124758520356</v>
       </c>
-      <c r="AG88" s="99" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH88" s="100"/>
-      <c r="AI88" s="100"/>
-      <c r="AJ88" s="100"/>
-      <c r="AK88" s="100"/>
-      <c r="AL88" s="100"/>
-      <c r="AM88" s="101"/>
+      <c r="AG88"/>
+      <c r="AH88"/>
+      <c r="AI88"/>
+      <c r="AJ88"/>
+      <c r="AK88"/>
+      <c r="AL88"/>
+      <c r="AM88"/>
+      <c r="AN88"/>
+      <c r="AO88"/>
     </row>
     <row r="89" spans="23:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W89" s="83"/>
-      <c r="X89" s="88"/>
+      <c r="W89" s="70"/>
+      <c r="X89" s="71"/>
       <c r="Y89" s="29">
         <v>8</v>
       </c>
@@ -6069,24 +5748,26 @@
       </c>
       <c r="AC89" s="36"/>
       <c r="AD89" s="59">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>-72.130208034844401</v>
       </c>
       <c r="AE89" s="56">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>-70.440413993126612</v>
       </c>
-      <c r="AG89" s="102"/>
-      <c r="AH89" s="103"/>
-      <c r="AI89" s="103"/>
-      <c r="AJ89" s="103"/>
-      <c r="AK89" s="103"/>
-      <c r="AL89" s="103"/>
-      <c r="AM89" s="104"/>
+      <c r="AG89"/>
+      <c r="AH89"/>
+      <c r="AI89"/>
+      <c r="AJ89"/>
+      <c r="AK89"/>
+      <c r="AL89"/>
+      <c r="AM89"/>
+      <c r="AN89"/>
+      <c r="AO89"/>
     </row>
     <row r="90" spans="23:41" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="W90" s="85"/>
-      <c r="X90" s="89"/>
+      <c r="W90" s="72"/>
+      <c r="X90" s="73"/>
       <c r="Y90" s="43">
         <v>16</v>
       </c>
@@ -6110,832 +5791,626 @@
         <f>(AA90-AA69)/AA69*100</f>
         <v>-66.460409300332159</v>
       </c>
-      <c r="AG90" s="105"/>
-      <c r="AH90" s="106"/>
-      <c r="AI90" s="106"/>
-      <c r="AJ90" s="106"/>
-      <c r="AK90" s="106"/>
-      <c r="AL90" s="106"/>
-      <c r="AM90" s="107"/>
-    </row>
-    <row r="91" spans="23:41" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AG91" s="81" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH91" s="82"/>
-      <c r="AI91" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ91" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK91" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL91" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM91" s="34" t="s">
-        <v>59</v>
-      </c>
+      <c r="AG90"/>
+      <c r="AH90"/>
+      <c r="AI90"/>
+      <c r="AJ90"/>
+      <c r="AK90"/>
+      <c r="AL90"/>
+      <c r="AM90"/>
+      <c r="AN90"/>
+      <c r="AO90"/>
+    </row>
+    <row r="91" spans="23:41" x14ac:dyDescent="0.3">
+      <c r="AG91"/>
+      <c r="AH91"/>
+      <c r="AI91"/>
+      <c r="AJ91"/>
+      <c r="AK91"/>
+      <c r="AL91"/>
+      <c r="AM91"/>
+      <c r="AN91"/>
+      <c r="AO91"/>
     </row>
     <row r="92" spans="23:41" x14ac:dyDescent="0.3">
-      <c r="AG92" s="83"/>
-      <c r="AH92" s="84"/>
-      <c r="AI92" s="21">
-        <v>2</v>
-      </c>
-      <c r="AJ92" s="20">
+      <c r="AG92"/>
+      <c r="AH92"/>
+      <c r="AI92"/>
+      <c r="AJ92"/>
+      <c r="AK92"/>
+      <c r="AL92"/>
+      <c r="AM92"/>
+      <c r="AN92"/>
+      <c r="AO92"/>
+    </row>
+    <row r="93" spans="23:41" x14ac:dyDescent="0.3">
+      <c r="AG93"/>
+      <c r="AH93"/>
+      <c r="AI93"/>
+      <c r="AJ93"/>
+      <c r="AK93"/>
+      <c r="AL93"/>
+      <c r="AM93"/>
+      <c r="AN93"/>
+      <c r="AO93"/>
+    </row>
+    <row r="94" spans="23:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG94"/>
+      <c r="AH94"/>
+      <c r="AI94"/>
+      <c r="AJ94"/>
+      <c r="AK94"/>
+      <c r="AL94"/>
+      <c r="AM94"/>
+      <c r="AN94"/>
+      <c r="AO94"/>
+    </row>
+    <row r="95" spans="23:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG95"/>
+      <c r="AH95"/>
+      <c r="AI95"/>
+      <c r="AJ95"/>
+      <c r="AK95"/>
+      <c r="AL95"/>
+      <c r="AM95"/>
+      <c r="AN95"/>
+      <c r="AO95"/>
+    </row>
+    <row r="96" spans="23:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG96"/>
+      <c r="AH96"/>
+      <c r="AI96"/>
+      <c r="AJ96"/>
+      <c r="AK96"/>
+      <c r="AL96"/>
+      <c r="AM96"/>
+      <c r="AN96"/>
+      <c r="AO96"/>
+    </row>
+    <row r="97" spans="33:49" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG97"/>
+      <c r="AH97"/>
+      <c r="AI97"/>
+      <c r="AJ97"/>
+      <c r="AK97"/>
+      <c r="AL97"/>
+      <c r="AM97"/>
+      <c r="AN97"/>
+      <c r="AO97"/>
+    </row>
+    <row r="98" spans="33:49" x14ac:dyDescent="0.3">
+      <c r="AG98"/>
+      <c r="AH98"/>
+      <c r="AI98"/>
+      <c r="AJ98"/>
+      <c r="AK98"/>
+      <c r="AL98"/>
+      <c r="AM98"/>
+      <c r="AN98"/>
+      <c r="AO98"/>
+    </row>
+    <row r="99" spans="33:49" x14ac:dyDescent="0.3">
+      <c r="AG99"/>
+      <c r="AH99"/>
+      <c r="AI99"/>
+      <c r="AJ99"/>
+      <c r="AK99"/>
+      <c r="AL99"/>
+      <c r="AM99"/>
+      <c r="AN99"/>
+      <c r="AO99"/>
+    </row>
+    <row r="100" spans="33:49" x14ac:dyDescent="0.3">
+      <c r="AG100"/>
+      <c r="AH100"/>
+      <c r="AI100"/>
+      <c r="AJ100"/>
+      <c r="AK100"/>
+      <c r="AL100"/>
+      <c r="AM100"/>
+      <c r="AN100"/>
+      <c r="AO100"/>
+    </row>
+    <row r="101" spans="33:49" x14ac:dyDescent="0.3">
+      <c r="AG101"/>
+      <c r="AH101"/>
+      <c r="AI101"/>
+      <c r="AJ101"/>
+      <c r="AK101"/>
+      <c r="AL101"/>
+      <c r="AM101"/>
+      <c r="AN101"/>
+      <c r="AO101"/>
+    </row>
+    <row r="102" spans="33:49" x14ac:dyDescent="0.3">
+      <c r="AG102"/>
+      <c r="AH102"/>
+      <c r="AI102"/>
+      <c r="AJ102"/>
+      <c r="AK102"/>
+      <c r="AL102"/>
+      <c r="AM102"/>
+      <c r="AN102"/>
+      <c r="AO102"/>
+    </row>
+    <row r="103" spans="33:49" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG103"/>
+      <c r="AH103"/>
+      <c r="AI103"/>
+      <c r="AJ103"/>
+      <c r="AK103"/>
+      <c r="AL103"/>
+      <c r="AM103"/>
+      <c r="AN103"/>
+      <c r="AO103"/>
+    </row>
+    <row r="104" spans="33:49" x14ac:dyDescent="0.3">
+      <c r="AG104"/>
+      <c r="AH104"/>
+      <c r="AI104"/>
+      <c r="AJ104"/>
+      <c r="AK104"/>
+      <c r="AL104"/>
+      <c r="AM104"/>
+      <c r="AN104"/>
+      <c r="AO104"/>
+    </row>
+    <row r="108" spans="33:49" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG108" s="129" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH108" s="129"/>
+      <c r="AI108" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ108" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK108" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL108" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="AM108" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN108" s="62"/>
+      <c r="AO108" s="62"/>
+      <c r="AQ108" s="130" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR108" s="130"/>
+      <c r="AS108" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT108" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU108" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV108" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="AW108" s="63" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="109" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG109" s="129" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH109" s="129"/>
+      <c r="AI109" s="65">
+        <v>2</v>
+      </c>
+      <c r="AJ109" s="65">
         <v>18809</v>
       </c>
-      <c r="AK92" s="20">
+      <c r="AK109" s="65">
         <v>17887</v>
       </c>
-      <c r="AL92" s="37">
+      <c r="AL109" s="65">
         <v>417</v>
       </c>
-      <c r="AM92" s="22">
+      <c r="AM109" s="65">
         <v>25</v>
       </c>
-    </row>
-    <row r="93" spans="23:41" x14ac:dyDescent="0.3">
-      <c r="AG93" s="83"/>
-      <c r="AH93" s="84"/>
-      <c r="AI93" s="4">
+      <c r="AN109" s="62"/>
+      <c r="AO109" s="62"/>
+      <c r="AQ109" s="131" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR109" s="132"/>
+      <c r="AS109" s="65">
+        <v>2</v>
+      </c>
+      <c r="AT109" s="65">
+        <v>141432</v>
+      </c>
+      <c r="AU109" s="65">
+        <v>141913</v>
+      </c>
+      <c r="AV109" s="65">
+        <v>306</v>
+      </c>
+      <c r="AW109" s="65">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="110" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG110" s="129"/>
+      <c r="AH110" s="129"/>
+      <c r="AI110" s="65">
         <v>3</v>
       </c>
-      <c r="AJ93" s="2">
+      <c r="AJ110" s="65">
         <v>23475</v>
       </c>
-      <c r="AK93" s="2">
+      <c r="AK110" s="65">
         <v>34593</v>
       </c>
-      <c r="AL93" s="2">
+      <c r="AL110" s="65">
         <v>316</v>
       </c>
-      <c r="AM93" s="5">
+      <c r="AM110" s="65">
         <v>31</v>
       </c>
-    </row>
-    <row r="94" spans="23:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG94" s="83"/>
-      <c r="AH94" s="84"/>
-      <c r="AI94" s="4">
-        <v>4</v>
-      </c>
-      <c r="AJ94" s="2">
+      <c r="AN110" s="62"/>
+      <c r="AO110" s="62"/>
+      <c r="AQ110" s="133"/>
+      <c r="AR110" s="134"/>
+      <c r="AS110" s="65">
+        <v>3</v>
+      </c>
+      <c r="AT110" s="65">
+        <v>227005</v>
+      </c>
+      <c r="AU110" s="65">
+        <v>245202</v>
+      </c>
+      <c r="AV110" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW110" s="65">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="111" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG111" s="129"/>
+      <c r="AH111" s="129"/>
+      <c r="AI111" s="65">
+        <v>4</v>
+      </c>
+      <c r="AJ111" s="65">
         <v>30121</v>
       </c>
-      <c r="AK94" s="2">
+      <c r="AK111" s="65">
         <v>40791</v>
       </c>
-      <c r="AL94" s="36">
+      <c r="AL111" s="65">
         <v>315</v>
       </c>
-      <c r="AM94" s="5">
+      <c r="AM111" s="65">
         <v>31</v>
       </c>
-    </row>
-    <row r="95" spans="23:41" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG95" s="83"/>
-      <c r="AH95" s="84"/>
-      <c r="AI95" s="29">
+      <c r="AN111" s="62"/>
+      <c r="AO111" s="62"/>
+      <c r="AQ111" s="130" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR111" s="130"/>
+      <c r="AS111" s="65">
+        <v>2</v>
+      </c>
+      <c r="AT111" s="65">
+        <v>33202</v>
+      </c>
+      <c r="AU111" s="65">
+        <v>99066</v>
+      </c>
+      <c r="AV111" s="65">
+        <v>351</v>
+      </c>
+      <c r="AW111" s="65">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="112" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG112" s="129"/>
+      <c r="AH112" s="129"/>
+      <c r="AI112" s="64">
         <v>5</v>
       </c>
-      <c r="AJ95" s="2">
+      <c r="AJ112" s="65">
         <v>28924</v>
       </c>
-      <c r="AK95" s="2">
+      <c r="AK112" s="65">
         <v>41929</v>
       </c>
-      <c r="AL95" s="36">
+      <c r="AL112" s="65">
         <v>305</v>
       </c>
-      <c r="AM95" s="5">
+      <c r="AM112" s="65">
         <v>40</v>
       </c>
-    </row>
-    <row r="96" spans="23:41" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG96" s="83"/>
-      <c r="AH96" s="84"/>
-      <c r="AI96" s="39">
-        <v>8</v>
-      </c>
-      <c r="AJ96" s="40">
+      <c r="AN112" s="62"/>
+      <c r="AQ112" s="130"/>
+      <c r="AR112" s="130"/>
+      <c r="AS112" s="65">
+        <v>3</v>
+      </c>
+      <c r="AT112" s="65">
+        <v>44398</v>
+      </c>
+      <c r="AU112" s="65">
+        <v>133626</v>
+      </c>
+      <c r="AV112" s="65">
+        <v>305</v>
+      </c>
+      <c r="AW112" s="65">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="113" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG113" s="129"/>
+      <c r="AH113" s="129"/>
+      <c r="AI113" s="64">
+        <v>8</v>
+      </c>
+      <c r="AJ113" s="65">
         <v>34898</v>
       </c>
-      <c r="AK96" s="40">
+      <c r="AK113" s="65">
         <v>50339</v>
       </c>
-      <c r="AL96" s="41">
+      <c r="AL113" s="65">
+        <v>322</v>
+      </c>
+      <c r="AM113" s="65">
+        <v>44</v>
+      </c>
+      <c r="AN113" s="62"/>
+      <c r="AQ113" s="130"/>
+      <c r="AR113" s="130"/>
+      <c r="AS113" s="65">
+        <v>4</v>
+      </c>
+      <c r="AT113" s="65">
+        <v>58104</v>
+      </c>
+      <c r="AU113" s="65">
+        <v>162790</v>
+      </c>
+      <c r="AV113" s="65">
+        <v>302</v>
+      </c>
+      <c r="AW113" s="65">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="114" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG114" s="129"/>
+      <c r="AH114" s="129"/>
+      <c r="AI114" s="64">
+        <v>16</v>
+      </c>
+      <c r="AJ114" s="65">
+        <v>56858</v>
+      </c>
+      <c r="AK114" s="65">
+        <v>74664</v>
+      </c>
+      <c r="AL114" s="65">
         <v>329</v>
       </c>
-      <c r="AM96" s="42">
+      <c r="AM114" s="65">
         <v>44</v>
       </c>
-    </row>
-    <row r="97" spans="33:49" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AG97" s="85"/>
-      <c r="AH97" s="86"/>
-      <c r="AI97" s="30">
-        <v>16</v>
-      </c>
-      <c r="AJ97" s="7">
-        <v>56858</v>
-      </c>
-      <c r="AK97" s="7">
-        <v>74664</v>
-      </c>
-      <c r="AL97" s="7">
-        <v>319</v>
-      </c>
-      <c r="AM97" s="8">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="98" spans="33:49" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AG98" s="81" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH98" s="87"/>
-      <c r="AI98" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ98" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK98" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL98" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM98" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="AN98" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO98" s="34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AG99" s="83"/>
-      <c r="AH99" s="88"/>
-      <c r="AI99" s="35">
-        <v>2</v>
-      </c>
-      <c r="AJ99" s="27">
+      <c r="AN114" s="62"/>
+      <c r="AQ114" s="130"/>
+      <c r="AR114" s="130"/>
+      <c r="AS114" s="65">
+        <v>5</v>
+      </c>
+      <c r="AT114" s="65">
+        <v>91843</v>
+      </c>
+      <c r="AU114" s="65">
+        <v>202514</v>
+      </c>
+      <c r="AV114" s="65">
+        <v>300</v>
+      </c>
+      <c r="AW114" s="65">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="115" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG115" s="129" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH115" s="129"/>
+      <c r="AI115" s="65">
+        <v>2</v>
+      </c>
+      <c r="AJ115" s="65">
         <v>5301</v>
       </c>
-      <c r="AK99" s="27">
+      <c r="AK115" s="65">
         <v>7205</v>
       </c>
-      <c r="AL99" s="51">
-        <v>470</v>
-      </c>
-      <c r="AM99" s="51">
-        <f>AM92+17</f>
-        <v>42</v>
-      </c>
-      <c r="AN99" s="59">
-        <f>-(AJ92-AJ99)/AJ92*100</f>
-        <v>-71.816683502578542</v>
-      </c>
-      <c r="AO99" s="56">
-        <f>-(AK92-AK99)/AK92*100</f>
-        <v>-59.719349248057249</v>
-      </c>
-    </row>
-    <row r="100" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AG100" s="83"/>
-      <c r="AH100" s="88"/>
-      <c r="AI100" s="4">
-        <v>3</v>
-      </c>
-      <c r="AJ100" s="2">
-        <v>6123</v>
-      </c>
-      <c r="AK100" s="2">
-        <v>9599</v>
-      </c>
-      <c r="AL100" s="2">
-        <v>321</v>
-      </c>
-      <c r="AM100" s="51">
-        <f t="shared" ref="AM100:AM104" si="14">AM93+17</f>
-        <v>48</v>
-      </c>
-      <c r="AN100" s="59">
-        <f t="shared" ref="AN100:AN104" si="15">-(AJ93-AJ100)/AJ93*100</f>
-        <v>-73.91693290734824</v>
-      </c>
-      <c r="AO100" s="56">
-        <f t="shared" ref="AO100:AO104" si="16">-(AK93-AK100)/AK93*100</f>
-        <v>-72.251611597722089</v>
-      </c>
-    </row>
-    <row r="101" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AG101" s="83"/>
-      <c r="AH101" s="88"/>
-      <c r="AI101" s="4">
-        <v>4</v>
-      </c>
-      <c r="AJ101" s="2">
-        <v>7589</v>
-      </c>
-      <c r="AK101" s="2">
-        <v>11758</v>
-      </c>
-      <c r="AL101" s="36">
-        <v>312</v>
-      </c>
-      <c r="AM101" s="51">
-        <f t="shared" si="14"/>
-        <v>48</v>
-      </c>
-      <c r="AN101" s="59">
-        <f t="shared" si="15"/>
-        <v>-74.804953354802294</v>
-      </c>
-      <c r="AO101" s="56">
-        <f t="shared" si="16"/>
-        <v>-71.175014096246727</v>
-      </c>
-    </row>
-    <row r="102" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AG102" s="83"/>
-      <c r="AH102" s="88"/>
-      <c r="AI102" s="29">
-        <v>5</v>
-      </c>
-      <c r="AJ102" s="2">
-        <v>8278</v>
-      </c>
-      <c r="AK102" s="2">
-        <v>12595</v>
-      </c>
-      <c r="AL102" s="36">
-        <v>308</v>
-      </c>
-      <c r="AM102" s="51">
-        <f t="shared" si="14"/>
-        <v>57</v>
-      </c>
-      <c r="AN102" s="59">
-        <f t="shared" si="15"/>
-        <v>-71.380168718019647</v>
-      </c>
-      <c r="AO102" s="56">
-        <f t="shared" si="16"/>
-        <v>-69.961124758520356</v>
-      </c>
-    </row>
-    <row r="103" spans="33:49" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG103" s="83"/>
-      <c r="AH103" s="88"/>
-      <c r="AI103" s="29">
-        <v>8</v>
-      </c>
-      <c r="AJ103" s="2">
-        <v>9726</v>
-      </c>
-      <c r="AK103" s="2">
-        <v>14880</v>
-      </c>
-      <c r="AL103" s="36">
-        <v>322</v>
-      </c>
-      <c r="AM103" s="51">
-        <f t="shared" si="14"/>
-        <v>61</v>
-      </c>
-      <c r="AN103" s="59">
-        <f t="shared" si="15"/>
-        <v>-72.130208034844401</v>
-      </c>
-      <c r="AO103" s="56">
-        <f t="shared" si="16"/>
-        <v>-70.440413993126612</v>
-      </c>
-    </row>
-    <row r="104" spans="33:49" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AG104" s="85"/>
-      <c r="AH104" s="89"/>
-      <c r="AI104" s="43">
-        <v>16</v>
-      </c>
-      <c r="AJ104" s="44">
-        <v>16113</v>
-      </c>
-      <c r="AK104" s="44">
-        <v>25042</v>
-      </c>
-      <c r="AL104" s="45">
-        <v>368</v>
-      </c>
-      <c r="AM104" s="51">
-        <f t="shared" si="14"/>
-        <v>61</v>
-      </c>
-      <c r="AN104" s="59">
-        <f t="shared" si="15"/>
-        <v>-71.660979985226362</v>
-      </c>
-      <c r="AO104" s="56">
-        <f t="shared" si="16"/>
-        <v>-66.460409300332159</v>
-      </c>
-    </row>
-    <row r="108" spans="33:49" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG108" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH108" s="80"/>
-      <c r="AI108" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ108" s="76" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK108" s="76" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL108" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM108" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN108" s="72"/>
-      <c r="AO108" s="72"/>
-      <c r="AQ108" s="79" t="s">
-        <v>77</v>
-      </c>
-      <c r="AR108" s="79"/>
-      <c r="AS108" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="AT108" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU108" s="75" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV108" s="75" t="s">
-        <v>76</v>
-      </c>
-      <c r="AW108" s="75" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="109" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG109" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH109" s="80"/>
-      <c r="AI109" s="77">
-        <v>2</v>
-      </c>
-      <c r="AJ109" s="77">
-        <v>18809</v>
-      </c>
-      <c r="AK109" s="77">
-        <v>17887</v>
-      </c>
-      <c r="AL109" s="77">
-        <v>417</v>
-      </c>
-      <c r="AM109" s="77">
-        <v>25</v>
-      </c>
-      <c r="AN109" s="72"/>
-      <c r="AO109" s="72"/>
-      <c r="AQ109" s="148" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR109" s="149"/>
-      <c r="AS109" s="77">
-        <v>2</v>
-      </c>
-      <c r="AT109" s="77">
-        <v>141432</v>
-      </c>
-      <c r="AU109" s="77">
-        <v>141913</v>
-      </c>
-      <c r="AV109" s="77">
-        <v>306</v>
-      </c>
-      <c r="AW109" s="77">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="110" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG110" s="80"/>
-      <c r="AH110" s="80"/>
-      <c r="AI110" s="77">
-        <v>3</v>
-      </c>
-      <c r="AJ110" s="77">
-        <v>23475</v>
-      </c>
-      <c r="AK110" s="77">
-        <v>34593</v>
-      </c>
-      <c r="AL110" s="77">
-        <v>316</v>
-      </c>
-      <c r="AM110" s="77">
-        <v>31</v>
-      </c>
-      <c r="AN110" s="72"/>
-      <c r="AO110" s="72"/>
-      <c r="AQ110" s="150"/>
-      <c r="AR110" s="151"/>
-      <c r="AS110" s="77">
-        <v>3</v>
-      </c>
-      <c r="AT110" s="77">
-        <v>227005</v>
-      </c>
-      <c r="AU110" s="77">
-        <v>245202</v>
-      </c>
-      <c r="AV110" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW110" s="77">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="111" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG111" s="80"/>
-      <c r="AH111" s="80"/>
-      <c r="AI111" s="77">
-        <v>4</v>
-      </c>
-      <c r="AJ111" s="77">
-        <v>30121</v>
-      </c>
-      <c r="AK111" s="77">
-        <v>40791</v>
-      </c>
-      <c r="AL111" s="77">
-        <v>315</v>
-      </c>
-      <c r="AM111" s="77">
-        <v>31</v>
-      </c>
-      <c r="AN111" s="72"/>
-      <c r="AO111" s="72"/>
-      <c r="AQ111" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR111" s="79"/>
-      <c r="AS111" s="77">
-        <v>2</v>
-      </c>
-      <c r="AT111" s="77">
-        <v>33202</v>
-      </c>
-      <c r="AU111" s="77">
-        <v>99066</v>
-      </c>
-      <c r="AV111" s="77">
-        <v>351</v>
-      </c>
-      <c r="AW111" s="77">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="112" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG112" s="80"/>
-      <c r="AH112" s="80"/>
-      <c r="AI112" s="76">
-        <v>5</v>
-      </c>
-      <c r="AJ112" s="77">
-        <v>28924</v>
-      </c>
-      <c r="AK112" s="77">
-        <v>41929</v>
-      </c>
-      <c r="AL112" s="77">
-        <v>305</v>
-      </c>
-      <c r="AM112" s="77">
-        <v>40</v>
-      </c>
-      <c r="AN112" s="72"/>
-      <c r="AQ112" s="79"/>
-      <c r="AR112" s="79"/>
-      <c r="AS112" s="77">
-        <v>3</v>
-      </c>
-      <c r="AT112" s="77">
-        <v>44398</v>
-      </c>
-      <c r="AU112" s="77">
-        <v>133626</v>
-      </c>
-      <c r="AV112" s="77">
-        <v>305</v>
-      </c>
-      <c r="AW112" s="77">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="113" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG113" s="80"/>
-      <c r="AH113" s="80"/>
-      <c r="AI113" s="76">
-        <v>8</v>
-      </c>
-      <c r="AJ113" s="77">
-        <v>34898</v>
-      </c>
-      <c r="AK113" s="77">
-        <v>50339</v>
-      </c>
-      <c r="AL113" s="77">
-        <v>322</v>
-      </c>
-      <c r="AM113" s="77">
-        <v>44</v>
-      </c>
-      <c r="AN113" s="72"/>
-      <c r="AQ113" s="79"/>
-      <c r="AR113" s="79"/>
-      <c r="AS113" s="77">
-        <v>4</v>
-      </c>
-      <c r="AT113" s="77">
-        <v>58104</v>
-      </c>
-      <c r="AU113" s="77">
-        <v>162790</v>
-      </c>
-      <c r="AV113" s="77">
-        <v>302</v>
-      </c>
-      <c r="AW113" s="77">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="114" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG114" s="80"/>
-      <c r="AH114" s="80"/>
-      <c r="AI114" s="76">
-        <v>16</v>
-      </c>
-      <c r="AJ114" s="77">
-        <v>56858</v>
-      </c>
-      <c r="AK114" s="77">
-        <v>74664</v>
-      </c>
-      <c r="AL114" s="77">
-        <v>329</v>
-      </c>
-      <c r="AM114" s="77">
-        <v>44</v>
-      </c>
-      <c r="AN114" s="72"/>
-      <c r="AQ114" s="79"/>
-      <c r="AR114" s="79"/>
-      <c r="AS114" s="77">
-        <v>5</v>
-      </c>
-      <c r="AT114" s="77">
-        <v>91843</v>
-      </c>
-      <c r="AU114" s="77">
-        <v>202514</v>
-      </c>
-      <c r="AV114" s="77">
-        <v>300</v>
-      </c>
-      <c r="AW114" s="77">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="115" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG115" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH115" s="80"/>
-      <c r="AI115" s="77">
-        <v>2</v>
-      </c>
-      <c r="AJ115" s="77">
-        <v>5301</v>
-      </c>
-      <c r="AK115" s="77">
-        <v>7205</v>
-      </c>
-      <c r="AL115" s="77">
+      <c r="AL115" s="65">
         <v>430</v>
       </c>
-      <c r="AM115" s="77">
+      <c r="AM115" s="65">
         <f>AM109+17</f>
         <v>42</v>
       </c>
-      <c r="AQ115" s="79"/>
-      <c r="AR115" s="79"/>
-      <c r="AS115" s="77">
-        <v>8</v>
-      </c>
-      <c r="AT115" s="77">
+      <c r="AQ115" s="130"/>
+      <c r="AR115" s="130"/>
+      <c r="AS115" s="65">
+        <v>8</v>
+      </c>
+      <c r="AT115" s="65">
         <v>105331</v>
       </c>
-      <c r="AU115" s="77">
+      <c r="AU115" s="65">
         <v>232964</v>
       </c>
-      <c r="AV115" s="77">
+      <c r="AV115" s="65">
         <v>309</v>
       </c>
-      <c r="AW115" s="77">
+      <c r="AW115" s="65">
         <v>189</v>
       </c>
     </row>
     <row r="116" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG116" s="80"/>
-      <c r="AH116" s="80"/>
-      <c r="AI116" s="77">
+      <c r="AG116" s="129"/>
+      <c r="AH116" s="129"/>
+      <c r="AI116" s="65">
         <v>3</v>
       </c>
-      <c r="AJ116" s="77">
+      <c r="AJ116" s="65">
         <v>6123</v>
       </c>
-      <c r="AK116" s="77">
+      <c r="AK116" s="65">
         <v>9599</v>
       </c>
-      <c r="AL116" s="77">
+      <c r="AL116" s="65">
         <v>321</v>
       </c>
-      <c r="AM116" s="77">
-        <f t="shared" ref="AM116:AM120" si="17">AM110+17</f>
+      <c r="AM116" s="65">
+        <f t="shared" ref="AM116:AM120" si="11">AM110+17</f>
         <v>48</v>
       </c>
-      <c r="AQ116" s="79"/>
-      <c r="AR116" s="79"/>
-      <c r="AS116" s="77">
+      <c r="AQ116" s="130"/>
+      <c r="AR116" s="130"/>
+      <c r="AS116" s="65">
         <v>16</v>
       </c>
-      <c r="AT116" s="77">
+      <c r="AT116" s="65">
         <v>262644</v>
       </c>
-      <c r="AU116" s="77">
+      <c r="AU116" s="65">
         <v>531764</v>
       </c>
-      <c r="AV116" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW116" s="77">
+      <c r="AV116" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW116" s="65">
         <v>224</v>
       </c>
     </row>
     <row r="117" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG117" s="80"/>
-      <c r="AH117" s="80"/>
-      <c r="AI117" s="77">
-        <v>4</v>
-      </c>
-      <c r="AJ117" s="77">
+      <c r="AG117" s="129"/>
+      <c r="AH117" s="129"/>
+      <c r="AI117" s="65">
+        <v>4</v>
+      </c>
+      <c r="AJ117" s="65">
         <v>7589</v>
       </c>
-      <c r="AK117" s="77">
+      <c r="AK117" s="65">
         <v>11758</v>
       </c>
-      <c r="AL117" s="77">
+      <c r="AL117" s="65">
         <v>317</v>
       </c>
-      <c r="AM117" s="77">
-        <f t="shared" si="17"/>
+      <c r="AM117" s="65">
+        <f t="shared" si="11"/>
         <v>48</v>
       </c>
     </row>
     <row r="118" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG118" s="80"/>
-      <c r="AH118" s="80"/>
-      <c r="AI118" s="76">
+      <c r="AG118" s="129"/>
+      <c r="AH118" s="129"/>
+      <c r="AI118" s="64">
         <v>5</v>
       </c>
-      <c r="AJ118" s="77">
+      <c r="AJ118" s="65">
         <v>8278</v>
       </c>
-      <c r="AK118" s="77">
+      <c r="AK118" s="65">
         <v>12595</v>
       </c>
-      <c r="AL118" s="77">
+      <c r="AL118" s="65">
         <v>308</v>
       </c>
-      <c r="AM118" s="77">
-        <f t="shared" si="17"/>
+      <c r="AM118" s="65">
+        <f t="shared" si="11"/>
         <v>57</v>
       </c>
     </row>
     <row r="119" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG119" s="80"/>
-      <c r="AH119" s="80"/>
-      <c r="AI119" s="76">
-        <v>8</v>
-      </c>
-      <c r="AJ119" s="77">
+      <c r="AG119" s="129"/>
+      <c r="AH119" s="129"/>
+      <c r="AI119" s="64">
+        <v>8</v>
+      </c>
+      <c r="AJ119" s="65">
         <v>9726</v>
       </c>
-      <c r="AK119" s="77">
+      <c r="AK119" s="65">
         <v>14880</v>
       </c>
-      <c r="AL119" s="77">
+      <c r="AL119" s="65">
         <v>322</v>
       </c>
-      <c r="AM119" s="77">
-        <f t="shared" si="17"/>
+      <c r="AM119" s="65">
+        <f t="shared" si="11"/>
         <v>61</v>
       </c>
     </row>
     <row r="120" spans="33:49" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AG120" s="80"/>
-      <c r="AH120" s="80"/>
-      <c r="AI120" s="76">
+      <c r="AG120" s="129"/>
+      <c r="AH120" s="129"/>
+      <c r="AI120" s="64">
         <v>16</v>
       </c>
-      <c r="AJ120" s="77">
+      <c r="AJ120" s="65">
         <v>16113</v>
       </c>
-      <c r="AK120" s="77">
+      <c r="AK120" s="65">
         <v>25042</v>
       </c>
-      <c r="AL120" s="77">
+      <c r="AL120" s="65">
         <v>368</v>
       </c>
-      <c r="AM120" s="77">
-        <f t="shared" si="17"/>
+      <c r="AM120" s="65">
+        <f t="shared" si="11"/>
         <v>61</v>
       </c>
     </row>
+    <row r="121" spans="33:49" x14ac:dyDescent="0.3">
+      <c r="AN121"/>
+      <c r="AO121"/>
+    </row>
     <row r="122" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AN122" s="73">
-        <f t="shared" ref="AN122:AO127" si="18">-(AJ109-AJ115)/AJ109*100</f>
-        <v>-71.816683502578542</v>
-      </c>
-      <c r="AO122" s="74">
-        <f t="shared" si="18"/>
-        <v>-59.719349248057249</v>
-      </c>
+      <c r="AN122"/>
+      <c r="AO122"/>
     </row>
     <row r="123" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AN123" s="73">
-        <f t="shared" si="18"/>
-        <v>-73.91693290734824</v>
-      </c>
-      <c r="AO123" s="74">
-        <f t="shared" si="18"/>
-        <v>-72.251611597722089</v>
-      </c>
+      <c r="AN123"/>
+      <c r="AO123"/>
     </row>
     <row r="124" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AN124" s="73">
-        <f t="shared" si="18"/>
-        <v>-74.804953354802294</v>
-      </c>
-      <c r="AO124" s="74">
-        <f t="shared" si="18"/>
-        <v>-71.175014096246727</v>
-      </c>
+      <c r="AN124"/>
+      <c r="AO124"/>
     </row>
     <row r="125" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AN125" s="73">
-        <f t="shared" si="18"/>
-        <v>-71.380168718019647</v>
-      </c>
-      <c r="AO125" s="74">
-        <f t="shared" si="18"/>
-        <v>-69.961124758520356</v>
-      </c>
+      <c r="AN125"/>
+      <c r="AO125"/>
     </row>
     <row r="126" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AN126" s="73">
-        <f t="shared" si="18"/>
-        <v>-72.130208034844401</v>
-      </c>
-      <c r="AO126" s="74">
-        <f t="shared" si="18"/>
-        <v>-70.440413993126612</v>
-      </c>
+      <c r="AN126"/>
+      <c r="AO126"/>
     </row>
     <row r="127" spans="33:49" x14ac:dyDescent="0.3">
-      <c r="AN127" s="73">
-        <f t="shared" si="18"/>
-        <v>-71.660979985226362</v>
-      </c>
-      <c r="AO127" s="74">
-        <f t="shared" si="18"/>
-        <v>-66.460409300332159</v>
-      </c>
+      <c r="AN127"/>
+      <c r="AO127"/>
       <c r="AQ127"/>
       <c r="AR127"/>
       <c r="AS127"/>
@@ -6963,256 +6438,256 @@
       <c r="AW129"/>
     </row>
     <row r="130" spans="43:51" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="AQ130" s="79" t="s">
-        <v>77</v>
-      </c>
-      <c r="AR130" s="79"/>
-      <c r="AS130" s="75" t="s">
+      <c r="AQ130" s="130" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR130" s="130"/>
+      <c r="AS130" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT130" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU130" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV130" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="AT130" s="75" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU130" s="75" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV130" s="75" t="s">
-        <v>76</v>
-      </c>
-      <c r="AW130" s="75" t="s">
-        <v>70</v>
+      <c r="AW130" s="63" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="131" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ131" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR131" s="79"/>
-      <c r="AS131" s="77">
-        <v>2</v>
-      </c>
-      <c r="AT131" s="77">
+      <c r="AQ131" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR131" s="130"/>
+      <c r="AS131" s="65">
+        <v>2</v>
+      </c>
+      <c r="AT131" s="65">
         <v>62764</v>
       </c>
-      <c r="AU131" s="77">
+      <c r="AU131" s="65">
         <v>59682</v>
       </c>
-      <c r="AV131" s="77">
+      <c r="AV131" s="65">
         <v>331</v>
       </c>
-      <c r="AW131" s="77">
+      <c r="AW131" s="65">
         <v>34</v>
       </c>
     </row>
     <row r="132" spans="43:51" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AQ132" s="79"/>
-      <c r="AR132" s="79"/>
-      <c r="AS132" s="77">
+      <c r="AQ132" s="130"/>
+      <c r="AR132" s="130"/>
+      <c r="AS132" s="65">
         <v>3</v>
       </c>
-      <c r="AT132" s="78">
+      <c r="AT132" s="66">
         <v>76297</v>
       </c>
-      <c r="AU132" s="78">
+      <c r="AU132" s="66">
         <v>82110</v>
       </c>
-      <c r="AV132" s="78">
+      <c r="AV132" s="66">
         <v>303</v>
       </c>
-      <c r="AW132" s="77">
+      <c r="AW132" s="65">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ133" s="79"/>
-      <c r="AR133" s="79"/>
-      <c r="AS133" s="77">
-        <v>4</v>
-      </c>
-      <c r="AT133" s="78">
+      <c r="AQ133" s="130"/>
+      <c r="AR133" s="130"/>
+      <c r="AS133" s="65">
+        <v>4</v>
+      </c>
+      <c r="AT133" s="66">
         <v>102637</v>
       </c>
-      <c r="AU133" s="78">
+      <c r="AU133" s="66">
         <v>103139</v>
       </c>
-      <c r="AV133" s="78">
+      <c r="AV133" s="66">
         <v>298</v>
       </c>
-      <c r="AW133" s="77">
+      <c r="AW133" s="65">
         <v>40</v>
       </c>
     </row>
     <row r="134" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ134" s="79"/>
-      <c r="AR134" s="79"/>
-      <c r="AS134" s="76">
+      <c r="AQ134" s="130"/>
+      <c r="AR134" s="130"/>
+      <c r="AS134" s="64">
         <v>5</v>
       </c>
-      <c r="AT134" s="78">
+      <c r="AT134" s="66">
         <v>157548</v>
       </c>
-      <c r="AU134" s="78">
+      <c r="AU134" s="66">
         <v>168731</v>
       </c>
-      <c r="AV134" s="78">
+      <c r="AV134" s="66">
         <v>310</v>
       </c>
-      <c r="AW134" s="77">
+      <c r="AW134" s="65">
         <f>78-26</f>
         <v>52</v>
       </c>
     </row>
     <row r="135" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ135" s="79"/>
-      <c r="AR135" s="79"/>
-      <c r="AS135" s="76">
-        <v>8</v>
-      </c>
-      <c r="AT135" s="77">
+      <c r="AQ135" s="130"/>
+      <c r="AR135" s="130"/>
+      <c r="AS135" s="64">
+        <v>8</v>
+      </c>
+      <c r="AT135" s="65">
         <v>186808</v>
       </c>
-      <c r="AU135" s="77">
+      <c r="AU135" s="65">
         <v>204566</v>
       </c>
-      <c r="AV135" s="77">
+      <c r="AV135" s="65">
         <v>308</v>
       </c>
-      <c r="AW135" s="77">
+      <c r="AW135" s="65">
         <v>57</v>
       </c>
     </row>
     <row r="136" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ136" s="79"/>
-      <c r="AR136" s="79"/>
-      <c r="AS136" s="77">
+      <c r="AQ136" s="130"/>
+      <c r="AR136" s="130"/>
+      <c r="AS136" s="65">
         <v>16</v>
       </c>
-      <c r="AT136" s="77">
+      <c r="AT136" s="65">
         <v>456817</v>
       </c>
-      <c r="AU136" s="77">
+      <c r="AU136" s="65">
         <v>448421</v>
       </c>
-      <c r="AV136" s="77" t="s">
+      <c r="AV136" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW136" s="65">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="137" spans="43:51" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AQ137" s="130" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR137" s="130"/>
+      <c r="AS137" s="65">
+        <v>2</v>
+      </c>
+      <c r="AT137" s="65">
+        <v>15702</v>
+      </c>
+      <c r="AU137" s="65">
+        <v>21154</v>
+      </c>
+      <c r="AV137" s="65">
+        <v>437</v>
+      </c>
+      <c r="AW137" s="65">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="138" spans="43:51" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AQ138" s="130"/>
+      <c r="AR138" s="130"/>
+      <c r="AS138" s="65">
+        <v>3</v>
+      </c>
+      <c r="AT138" s="66">
+        <v>18507</v>
+      </c>
+      <c r="AU138" s="66">
+        <v>27108</v>
+      </c>
+      <c r="AV138" s="66">
+        <v>311</v>
+      </c>
+      <c r="AW138" s="65">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="139" spans="43:51" x14ac:dyDescent="0.3">
+      <c r="AQ139" s="130"/>
+      <c r="AR139" s="130"/>
+      <c r="AS139" s="65">
+        <v>4</v>
+      </c>
+      <c r="AT139" s="66">
+        <v>23088</v>
+      </c>
+      <c r="AU139" s="66">
+        <v>33154</v>
+      </c>
+      <c r="AV139" s="66">
+        <v>305</v>
+      </c>
+      <c r="AW139" s="65">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="140" spans="43:51" x14ac:dyDescent="0.3">
+      <c r="AQ140" s="130"/>
+      <c r="AR140" s="130"/>
+      <c r="AS140" s="64">
+        <v>5</v>
+      </c>
+      <c r="AT140" s="65">
+        <v>30171</v>
+      </c>
+      <c r="AU140" s="65">
+        <v>41800</v>
+      </c>
+      <c r="AV140" s="65">
+        <v>297</v>
+      </c>
+      <c r="AW140" s="65">
         <v>78</v>
       </c>
-      <c r="AW136" s="77">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="137" spans="43:51" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AQ137" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR137" s="79"/>
-      <c r="AS137" s="77">
-        <v>2</v>
-      </c>
-      <c r="AT137" s="77">
-        <v>15702</v>
-      </c>
-      <c r="AU137" s="77">
-        <v>21154</v>
-      </c>
-      <c r="AV137" s="77">
-        <v>437</v>
-      </c>
-      <c r="AW137" s="77">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="138" spans="43:51" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="AQ138" s="79"/>
-      <c r="AR138" s="79"/>
-      <c r="AS138" s="77">
-        <v>3</v>
-      </c>
-      <c r="AT138" s="78">
-        <v>18507</v>
-      </c>
-      <c r="AU138" s="78">
-        <v>27108</v>
-      </c>
-      <c r="AV138" s="78">
-        <v>311</v>
-      </c>
-      <c r="AW138" s="77">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="139" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ139" s="79"/>
-      <c r="AR139" s="79"/>
-      <c r="AS139" s="77">
-        <v>4</v>
-      </c>
-      <c r="AT139" s="78">
-        <v>23088</v>
-      </c>
-      <c r="AU139" s="78">
-        <v>33154</v>
-      </c>
-      <c r="AV139" s="78">
-        <v>305</v>
-      </c>
-      <c r="AW139" s="77">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="140" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ140" s="79"/>
-      <c r="AR140" s="79"/>
-      <c r="AS140" s="76">
-        <v>5</v>
-      </c>
-      <c r="AT140" s="77">
-        <v>30171</v>
-      </c>
-      <c r="AU140" s="77">
-        <v>41800</v>
-      </c>
-      <c r="AV140" s="77">
-        <v>297</v>
-      </c>
-      <c r="AW140" s="77">
-        <v>78</v>
-      </c>
     </row>
     <row r="141" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ141" s="79"/>
-      <c r="AR141" s="79"/>
-      <c r="AS141" s="76">
-        <v>8</v>
-      </c>
-      <c r="AT141" s="77">
+      <c r="AQ141" s="130"/>
+      <c r="AR141" s="130"/>
+      <c r="AS141" s="64">
+        <v>8</v>
+      </c>
+      <c r="AT141" s="65">
         <v>36635</v>
       </c>
-      <c r="AU141" s="77">
+      <c r="AU141" s="65">
         <v>48979</v>
       </c>
-      <c r="AV141" s="77">
+      <c r="AV141" s="65">
         <v>309</v>
       </c>
-      <c r="AW141" s="77">
+      <c r="AW141" s="65">
         <v>83</v>
       </c>
     </row>
     <row r="142" spans="43:51" x14ac:dyDescent="0.3">
-      <c r="AQ142" s="79"/>
-      <c r="AR142" s="79"/>
-      <c r="AS142" s="77">
+      <c r="AQ142" s="130"/>
+      <c r="AR142" s="130"/>
+      <c r="AS142" s="65">
         <v>16</v>
       </c>
-      <c r="AT142" s="77">
+      <c r="AT142" s="65">
         <v>77215</v>
       </c>
-      <c r="AU142" s="77">
+      <c r="AU142" s="65">
         <v>104233</v>
       </c>
-      <c r="AV142" s="77">
+      <c r="AV142" s="65">
         <v>301</v>
       </c>
-      <c r="AW142" s="77">
+      <c r="AW142" s="65">
         <v>94</v>
       </c>
     </row>
@@ -7223,58 +6698,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="78">
-    <mergeCell ref="AG78:AH81"/>
-    <mergeCell ref="AG82:AH85"/>
-    <mergeCell ref="W77:X83"/>
-    <mergeCell ref="E38:F45"/>
-    <mergeCell ref="W84:X90"/>
-    <mergeCell ref="AG63:AH68"/>
-    <mergeCell ref="AG69:AH74"/>
-    <mergeCell ref="AG88:AM90"/>
-    <mergeCell ref="E30:F37"/>
-    <mergeCell ref="W60:AC62"/>
-    <mergeCell ref="W63:X69"/>
-    <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="S30:T37"/>
-    <mergeCell ref="E48:K50"/>
-    <mergeCell ref="E51:F57"/>
-    <mergeCell ref="E58:F64"/>
-    <mergeCell ref="N58:O64"/>
-    <mergeCell ref="AH18:AJ20"/>
-    <mergeCell ref="AE21:AF24"/>
-    <mergeCell ref="S27:AB29"/>
-    <mergeCell ref="W70:X76"/>
-    <mergeCell ref="S38:T45"/>
-    <mergeCell ref="AG60:AM62"/>
-    <mergeCell ref="AA18:AC20"/>
-    <mergeCell ref="AG75:AM77"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H4:J6"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="D4:G6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="W3:Y3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="H11:P11"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="T4:V6"/>
-    <mergeCell ref="Q4:S6"/>
-    <mergeCell ref="K4:M6"/>
-    <mergeCell ref="N4:P6"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="AC4:AE6"/>
-    <mergeCell ref="Z3:AB3"/>
-    <mergeCell ref="Z4:AB6"/>
-    <mergeCell ref="W4:Y6"/>
+  <mergeCells count="69">
+    <mergeCell ref="AQ137:AR142"/>
+    <mergeCell ref="AQ131:AR136"/>
+    <mergeCell ref="AQ111:AR116"/>
+    <mergeCell ref="AG109:AH114"/>
+    <mergeCell ref="AG115:AH120"/>
+    <mergeCell ref="AG108:AH108"/>
+    <mergeCell ref="AQ130:AR130"/>
+    <mergeCell ref="AQ109:AR110"/>
+    <mergeCell ref="AQ108:AR108"/>
     <mergeCell ref="E27:N29"/>
     <mergeCell ref="W51:X56"/>
     <mergeCell ref="W48:AE50"/>
@@ -7291,17 +6724,50 @@
     <mergeCell ref="K18:M20"/>
     <mergeCell ref="O21:P24"/>
     <mergeCell ref="X21:Y24"/>
-    <mergeCell ref="AG109:AH114"/>
-    <mergeCell ref="AG115:AH120"/>
-    <mergeCell ref="AG108:AH108"/>
-    <mergeCell ref="AQ130:AR130"/>
-    <mergeCell ref="AG91:AH97"/>
-    <mergeCell ref="AG98:AH104"/>
-    <mergeCell ref="AQ109:AR110"/>
-    <mergeCell ref="AQ108:AR108"/>
-    <mergeCell ref="AQ137:AR142"/>
-    <mergeCell ref="AQ131:AR136"/>
-    <mergeCell ref="AQ111:AR116"/>
+    <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="AC4:AE6"/>
+    <mergeCell ref="Z3:AB3"/>
+    <mergeCell ref="Z4:AB6"/>
+    <mergeCell ref="W4:Y6"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="H11:P11"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="T4:V6"/>
+    <mergeCell ref="Q4:S6"/>
+    <mergeCell ref="K4:M6"/>
+    <mergeCell ref="N4:P6"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H4:J6"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="D4:G6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="AH18:AJ20"/>
+    <mergeCell ref="AE21:AF24"/>
+    <mergeCell ref="S27:AB29"/>
+    <mergeCell ref="W70:X76"/>
+    <mergeCell ref="S38:T45"/>
+    <mergeCell ref="AA18:AC20"/>
+    <mergeCell ref="E30:F37"/>
+    <mergeCell ref="W60:AC62"/>
+    <mergeCell ref="W63:X69"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="S30:T37"/>
+    <mergeCell ref="E48:K50"/>
+    <mergeCell ref="E51:F57"/>
+    <mergeCell ref="E58:F64"/>
+    <mergeCell ref="N58:O64"/>
+    <mergeCell ref="W77:X83"/>
+    <mergeCell ref="E38:F45"/>
+    <mergeCell ref="W84:X90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
